--- a/data_raw/MLP_Itembank_3Ebenen.xlsx
+++ b/data_raw/MLP_Itembank_3Ebenen.xlsx
@@ -490,13 +490,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G671"/>
+  <dimension ref="A1:H671"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.86328125" defaultRowHeight="14.25"/>
   <cols>
     <col width="24.1328125" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="5"/>
+    <col width="70" customWidth="1" min="4" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -527,10 +527,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>shortscale</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>ref</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -559,10 +564,15 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Which of these statements describes best the individual interpretation and expression of the student?</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+          <t>Which of these statements describes best the **individual interpretation and expression** of the student?</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>Winter (1993) – Interpretation ("reflects musical understanding")</t>
         </is>
@@ -594,6 +604,11 @@
           <t>The playing conveys hardly any musical understanding. No feel for the character of the piece is recognisable.</t>
         </is>
       </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="27" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -621,6 +636,11 @@
           <t>The playing conveys only a rudimentary musical understanding. A feel for the character of the piece is rarely recognisable.</t>
         </is>
       </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="40.5" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -648,6 +668,11 @@
           <t>The playing conveys a partial musical understanding. A feel for the character of the piece is recognisable in some sections, but not in others.</t>
         </is>
       </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="40.5" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -675,6 +700,11 @@
           <t>The playing largely conveys a musical understanding and a feel for the character of the piece, whereas individual passages seem less considered.</t>
         </is>
       </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="27" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -702,6 +732,11 @@
           <t>The playing consistently conveys a deep musical understanding and a pronounced feel for the character of the piece.</t>
         </is>
       </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="40.5" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -721,12 +756,17 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist das **vermittelte musikalische Verständnis und Gespür für den Charakter des Werks** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist das vermittelte musikalische Verständnis und Gespür für den Charakter des Werks bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the musical understanding and feel for the character of the piece conveyed by the playing for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the musical understanding and feel for the character of the piece conveyed by the playing for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -756,6 +796,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -783,6 +828,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -810,6 +860,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -837,6 +892,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -864,6 +924,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="27" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -883,12 +948,17 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist das **vermittelte musikalische Verständnis und Gespür für den Charakter des Werks** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist das vermittelte musikalische Verständnis und Gespür für den Charakter des Werks bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the musical understanding and feel for the character of the piece conveyed by the playing for this pupil is:</t>
+          <t>**Compared to the last lesson**, the musical understanding and feel for the character of the piece conveyed by the playing for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -918,6 +988,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -945,6 +1020,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -972,6 +1052,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -999,6 +1084,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1026,6 +1116,11 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="27" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -1050,10 +1145,15 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Which of these statements describes best the individual interpretation and expression of the student?</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
+          <t>Which of these statements describes best the **individual interpretation and expression** of the student?</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>Thompson &amp; Williamon (2003) – Musicality ("stylistic accuracy")</t>
         </is>
@@ -1085,6 +1185,11 @@
           <t>The playing shows no recognisable understanding of the work's stylistic context.</t>
         </is>
       </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="27" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -1112,6 +1217,11 @@
           <t>The playing shows only a rudimentary understanding of the stylistic context; stylistic features are rarely taken into account.</t>
         </is>
       </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="27" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -1139,6 +1249,11 @@
           <t>The playing shows a basic understanding of the stylistic context, which is not consistently applied with nuance.</t>
         </is>
       </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="27" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -1166,6 +1281,11 @@
           <t>The playing largely shows an understanding of the stylistic context; individual stylistic details are not consistently realised.</t>
         </is>
       </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="27" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -1193,6 +1313,11 @@
           <t>The playing consistently shows a nuanced and confident understanding of the work's stylistic context.</t>
         </is>
       </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="27" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -1212,12 +1337,17 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist das **Verständnis des stilistischen Kontexts** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist das Verständnis des stilistischen Kontexts bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the understanding of the stylistic context for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the understanding of the stylistic context for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -1247,6 +1377,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1274,6 +1409,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1301,6 +1441,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1328,6 +1473,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1355,6 +1505,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="27" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -1374,12 +1529,17 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist das **Verständnis des stilistischen Kontexts** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist das Verständnis des stilistischen Kontexts bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the understanding of the stylistic context for this pupil is:</t>
+          <t>**Compared to the last lesson**, the understanding of the stylistic context for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -1409,6 +1569,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1436,6 +1601,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1463,6 +1633,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1490,6 +1665,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1517,6 +1697,11 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="27" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -1541,10 +1726,15 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Which of these statements describes best the individual interpretation and expression of the student?</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
+          <t>Which of these statements describes best **the individual interpretation and expression** of the student?</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>Thompson &amp; Williamon (2003) – Communication ("communication of emotional commitment and conviction")</t>
         </is>
@@ -1576,6 +1766,11 @@
           <t>The execution does not seem authentic or emotional; it remains purely technical and impersonal.</t>
         </is>
       </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="27" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -1603,6 +1798,11 @@
           <t>The execution seems only slightly authentic and emotional; a technical, impersonal execution predominates.</t>
         </is>
       </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="27" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
@@ -1630,6 +1830,11 @@
           <t>The execution seems partly authentic and emotional, but in other sections rather technical or detached.</t>
         </is>
       </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1657,6 +1862,11 @@
           <t>The execution is largely authentic and emotional.</t>
         </is>
       </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1684,6 +1894,11 @@
           <t>The execution is consistently authentic and emotionally moving.</t>
         </is>
       </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="27" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -1703,12 +1918,17 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Authentizität und emotionale Wirkung der Ausführung** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Authentizität und emotionale Wirkung der Ausführung bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the authenticity and emotional impact of the performance for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the authenticity and emotional impact of the performance for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -1738,6 +1958,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1765,6 +1990,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1792,6 +2022,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1819,6 +2054,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1846,6 +2086,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="27" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
@@ -1865,12 +2110,17 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Authentizität und emotionale Wirkung der Ausführung** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Authentizität und emotionale Wirkung der Ausführung bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the authenticity and emotional impact of the performance for this pupil is:</t>
+          <t>**Compared to the last lesson**, the authenticity and emotional impact of the performance for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -1900,6 +2150,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1927,6 +2182,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1954,6 +2214,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1981,6 +2246,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2008,6 +2278,11 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="27" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
@@ -2032,10 +2307,15 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Which of these statements applies to the overall quality of the instrumental performance?</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
+          <t>Which of these statements applies to the **overall quality of the instrumental performance**?</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
         <is>
           <t>Ciorba &amp; Smith (2009) – Multidimensional Assessment Rubric (kriterienbasierte Stufenbeschreibungen "meets minimal expectations…proficient")</t>
         </is>
@@ -2067,6 +2347,11 @@
           <t>The performance predominantly does not meet the standard defined for this level of achievement. Deviations are consistent and significantly shape the overall impression.</t>
         </is>
       </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="40.5" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
@@ -2094,6 +2379,11 @@
           <t>The performance only partially meets the standard. Frequent or repeated deviations are noticeable and clearly impair the overall impression.</t>
         </is>
       </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="40.5" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
@@ -2121,6 +2411,11 @@
           <t>The performance predominantly meets the standard. Recurring but not consistent deviations occur, occasionally diminishing the overall impression.</t>
         </is>
       </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="40.5" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
@@ -2148,6 +2443,11 @@
           <t>The performance meets the standard defined for this level of achievement. Isolated minor deviations are noticeable but do not impair the overall impression.</t>
         </is>
       </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="54" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
@@ -2175,6 +2475,11 @@
           <t>The performance consistently meets the standard defined for this level of achievement and exceeds it in individual aspects. Musical, technical and interpretive requirements are met confidently and with professional consistency.</t>
         </is>
       </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="27" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -2194,12 +2499,17 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Qualität der Darbietung** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Qualität der Darbietung bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the quality of the performance for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the quality of the performance for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -2229,6 +2539,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2256,6 +2571,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2283,6 +2603,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2310,6 +2635,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2337,6 +2667,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="27" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
@@ -2356,12 +2691,17 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Qualität der Darbietung** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Qualität der Darbietung bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the quality of the performance for this pupil is:</t>
+          <t>**Compared to the last lesson**, the quality of the performance for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -2391,6 +2731,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2418,6 +2763,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -2445,6 +2795,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -2472,6 +2827,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -2499,6 +2859,11 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="27" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
@@ -2523,10 +2888,15 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Which of these statements applies to the overall quality of the instrumental performance?</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
+          <t>Which of these statements applies to the **overall quality of the instrumental performance**?</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
         <is>
           <t>Thompson &amp; Williamon (2003) – Overall quality ("overall rating of performance quality"); auch Fiske (1975), Winter (1993) – Kategorie "overall"</t>
         </is>
@@ -2558,6 +2928,11 @@
           <t>The execution is predominantly not convincing. Consistent weaknesses in sound, technique or musical expression significantly shape the overall impression.</t>
         </is>
       </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="40.5" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
@@ -2585,6 +2960,11 @@
           <t>The execution is only somewhat convincing. Several aspects of the instrumental playing show clear weaknesses that noticeably impair the overall impression.</t>
         </is>
       </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="40.5" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
@@ -2612,6 +2992,11 @@
           <t>The execution is partially convincing. Some aspects succeed well, while recurring weaknesses in other areas occasionally diminish the overall impression.</t>
         </is>
       </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="27" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
@@ -2639,6 +3024,11 @@
           <t>The execution is convincing overall. Isolated minor weaknesses are noticeable but do not significantly diminish the positive overall impression.</t>
         </is>
       </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="40.5" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
@@ -2666,6 +3056,11 @@
           <t>The execution is consistently convincing at a high level. Sound, technique, rhythm and musical expression combine into a coherent, confident overall performance.</t>
         </is>
       </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="27" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
@@ -2685,12 +3080,17 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **generelle Ausführung des Instrumentalspiels** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die generelle Ausführung des Instrumentalspiels bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the overall execution of the instrumental playing for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the overall execution of the instrumental playing for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -2720,6 +3120,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -2747,6 +3152,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -2774,6 +3184,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -2801,6 +3216,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -2828,6 +3248,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="27" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
@@ -2847,12 +3272,17 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **generelle Ausführung des Instrumentalspiels** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die generelle Ausführung des Instrumentalspiels bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the overall execution of the instrumental playing for this pupil is:</t>
+          <t>**Compared to the last lesson**, the overall execution of the instrumental playing for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -2882,6 +3312,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -2909,6 +3344,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -2936,6 +3376,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -2963,6 +3408,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -2990,6 +3440,11 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -3014,10 +3469,15 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Which of these statements applies to the technical execution?</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
+          <t>Which of these statements applies to the **technical execution**?</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
         <is>
           <t>Abeles (1973) – Intonation ("the intonation was good"/"played out of tune")</t>
         </is>
@@ -3049,6 +3509,11 @@
           <t>The intonation is consistently inaccurate, regardless of the difficulty of the passage.</t>
         </is>
       </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="27" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
@@ -3076,6 +3541,11 @@
           <t>The intonation shows frequent deviations, especially in technically demanding passages.</t>
         </is>
       </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="27" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
@@ -3103,6 +3573,11 @@
           <t>The intonation is predominantly accurate but becomes noticeably unstable in technically demanding passages.</t>
         </is>
       </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="27" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
@@ -3130,6 +3605,11 @@
           <t>The intonation is largely accurate. Isolated, minor deviations occur in technically demanding passages.</t>
         </is>
       </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="27" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
@@ -3157,6 +3637,11 @@
           <t>The intonation is consistently accurate and remains fully stable even in technically demanding passages.</t>
         </is>
       </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="27" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
@@ -3176,12 +3661,17 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Treffsicherheit und Stabilität der Intonation** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Treffsicherheit und Stabilität der Intonation bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the accuracy and stability of the intonation for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the accuracy and stability of the intonation for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -3211,6 +3701,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -3238,6 +3733,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -3265,6 +3765,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -3292,6 +3797,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -3319,6 +3829,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="27" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
@@ -3338,12 +3853,17 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Treffsicherheit und Stabilität der Intonation** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Treffsicherheit und Stabilität der Intonation bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the accuracy and stability of the intonation for this pupil is:</t>
+          <t>**Compared to the last lesson**, the accuracy and stability of the intonation for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -3373,6 +3893,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -3400,6 +3925,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -3427,6 +3957,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -3454,6 +3989,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -3481,6 +4021,11 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -3505,7 +4050,12 @@
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>Which of these statements applies to the technical execution?</t>
+          <t>Which of these statements applies to the **technical execution**?</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -3535,7 +4085,12 @@
           <t>The rhythm is mostly played unclearly or imprecisely.</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
         <is>
           <t>Abeles (1973) – Rhythm-continuity; Saunders &amp; Holahan (1997) – Rhythmic accuracy</t>
         </is>
@@ -3567,6 +4122,11 @@
           <t>The rhythm is often imprecise: repeated rhythmic errors impair the overall impression.</t>
         </is>
       </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="27" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
@@ -3594,6 +4154,11 @@
           <t>The rhythm is predominantly recognisable but shows recurring inaccuracies.</t>
         </is>
       </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="27" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
@@ -3621,6 +4186,11 @@
           <t>The rhythm is largely clear and precise. Isolated minor inaccuracies are barely noticeable.</t>
         </is>
       </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -3648,6 +4218,11 @@
           <t>The rhythm is consistently played clearly and precisely.</t>
         </is>
       </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="27" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
@@ -3667,12 +4242,17 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Klarheit und Präzision des Rhythmus** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Klarheit und Präzision des Rhythmus bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the clarity and precision of the rhythm for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the clarity and precision of the rhythm for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -3702,6 +4282,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -3729,6 +4314,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -3756,6 +4346,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -3783,6 +4378,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -3810,6 +4410,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="27" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
@@ -3829,12 +4434,17 @@
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Klarheit und Präzision des Rhythmus** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Klarheit und Präzision des Rhythmus bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the clarity and precision of the rhythm for this pupil is:</t>
+          <t>**Compared to the last lesson**, the clarity and precision of the rhythm for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -3864,6 +4474,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -3891,6 +4506,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -3918,6 +4538,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -3945,6 +4570,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -3972,6 +4602,11 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -3996,10 +4631,15 @@
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>Which of these statements applies to the technical execution?</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
+          <t>Which of these statements applies to the **technical execution**?</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
         <is>
           <t>Saunders &amp; Holahan (1997) – Tempo ("is accurate and consistent with the printed tempo markings")</t>
         </is>
@@ -4031,6 +4671,11 @@
           <t>The tempo is consistently inconsistent or inappropriate for the piece.</t>
         </is>
       </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="27" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
@@ -4058,6 +4703,11 @@
           <t>The tempo fluctuates frequently or is only somewhat appropriate for the piece.</t>
         </is>
       </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="27" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
@@ -4085,6 +4735,11 @@
           <t>The tempo is partially consistent but fluctuates recurringly or is not consistently appropriate for the piece.</t>
         </is>
       </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="27" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
@@ -4112,6 +4767,11 @@
           <t>The tempo is largely consistent and appropriate; isolated minor fluctuations occur.</t>
         </is>
       </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="27" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
@@ -4139,6 +4799,11 @@
           <t>The tempo is consistently consistent and fully appropriate for the piece in every respect.</t>
         </is>
       </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="27" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
@@ -4158,12 +4823,17 @@
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Konsistenz und Angemessenheit des Tempos** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Konsistenz und Angemessenheit des Tempos bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the consistency and appropriateness of the tempo for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the consistency and appropriateness of the tempo for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -4193,6 +4863,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -4220,6 +4895,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -4247,6 +4927,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -4274,6 +4959,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -4301,6 +4991,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="27" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
@@ -4320,12 +5015,17 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Konsistenz und Angemessenheit des Tempos** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Konsistenz und Angemessenheit des Tempos bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the consistency and appropriateness of the tempo for this pupil is:</t>
+          <t>**Compared to the last lesson**, the consistency and appropriateness of the tempo for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -4355,6 +5055,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -4382,6 +5087,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -4409,6 +5119,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -4436,6 +5151,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -4463,6 +5183,11 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -4487,10 +5212,15 @@
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>Which of these statements applies to the technical execution?</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
+          <t>Which of these statements applies to the **technical execution**?</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
         <is>
           <t>Saunders &amp; Holahan (1997) – Technique/Articulation ("appropriate accents/slurs as marked")</t>
         </is>
@@ -4522,6 +5252,11 @@
           <t>The articulation is predominantly inconsistent and hardly corresponds to the recorded instructions.</t>
         </is>
       </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="27" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
@@ -4549,6 +5284,11 @@
           <t>The articulation frequently deviates from the recorded instructions or is inconsistent.</t>
         </is>
       </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="27" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
@@ -4576,6 +5316,11 @@
           <t>The articulation partially corresponds to the recorded instructions; recurring deviations are noticeable.</t>
         </is>
       </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="27" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
@@ -4603,6 +5348,11 @@
           <t>The articulation largely corresponds to the recorded instructions; isolated deviations are unobtrusive.</t>
         </is>
       </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="27" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
@@ -4630,6 +5380,11 @@
           <t>The articulation is consistently uniform and fully corresponds to the recorded instructions.</t>
         </is>
       </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="27" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
@@ -4649,12 +5404,17 @@
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Einheitlichkeit der Artikulation** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Einheitlichkeit der Artikulation bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the consistency of the articulation for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the consistency of the articulation for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -4684,6 +5444,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -4711,6 +5476,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -4738,6 +5508,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -4765,6 +5540,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -4792,6 +5572,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="27" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
@@ -4811,12 +5596,17 @@
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Einheitlichkeit der Artikulation** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Einheitlichkeit der Artikulation bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the consistency of the articulation for this pupil is:</t>
+          <t>**Compared to the last lesson**, the consistency of the articulation for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -4846,6 +5636,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -4873,6 +5668,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -4900,6 +5700,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -4927,6 +5732,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -4954,6 +5764,11 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -4978,10 +5793,15 @@
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>Which of these statements applies to the technical execution?</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
+          <t>Which of these statements applies to the **technical execution**?</t>
+        </is>
+      </c>
+      <c r="F164" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
         <is>
           <t>Saunders &amp; Holahan (1997) – Tone ("is full, rich, and characteristic of the tone quality of the instrument in all ranges")</t>
         </is>
@@ -5013,6 +5833,11 @@
           <t>The sound is predominantly thin, lacks resonance and is not characteristic of the instrument.</t>
         </is>
       </c>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="27" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
@@ -5040,6 +5865,11 @@
           <t>The sound is often lacking in resonance or only somewhat characteristic of the instrument.</t>
         </is>
       </c>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="27" customHeight="1">
       <c r="A167" s="2" t="inlineStr">
@@ -5067,6 +5897,11 @@
           <t>The sound is partially full and characteristic, but seems thin or unspecific in other sections.</t>
         </is>
       </c>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="27" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
@@ -5094,6 +5929,11 @@
           <t>The sound is largely full and characteristic of the instrument; in isolated moments it seems less resonant.</t>
         </is>
       </c>
+      <c r="F168" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="27" customHeight="1">
       <c r="A169" s="2" t="inlineStr">
@@ -5121,6 +5961,11 @@
           <t>The sound is consistently full, resonant and characteristic of the instrument.</t>
         </is>
       </c>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="27" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
@@ -5140,12 +5985,17 @@
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Fülle und Tragfähigkeit des Klangs** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Fülle und Tragfähigkeit des Klangs bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the fullness and resonance of the sound for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the fullness and resonance of the sound for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -5175,6 +6025,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -5202,6 +6057,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F172" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -5229,6 +6089,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -5256,6 +6121,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F174" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -5283,6 +6153,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="27" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
@@ -5302,12 +6177,17 @@
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Fülle und Tragfähigkeit des Klangs** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Fülle und Tragfähigkeit des Klangs bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the fullness and resonance of the sound for this pupil is:</t>
+          <t>**Compared to the last lesson**, the fullness and resonance of the sound for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F176" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -5337,6 +6217,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -5364,6 +6249,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F178" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -5391,6 +6281,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F179" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -5418,6 +6313,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F180" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -5445,6 +6345,11 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
+      <c r="F181" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -5469,15 +6374,20 @@
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>Which of these statements applies to the technical execution?</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
+          <t>Which of these statements applies to the **technical execution**?</t>
+        </is>
+      </c>
+      <c r="F182" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
         <is>
           <t>Ciorba &amp; Smith (2009) – Command of Instrument</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr">
+      <c r="H182" t="inlineStr">
         <is>
           <t>evtl. Item für Technik bei Kurzversion</t>
         </is>
@@ -5509,6 +6419,11 @@
           <t>The technical skills are predominantly insufficient for the level of difficulty.</t>
         </is>
       </c>
+      <c r="F183" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="27" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
@@ -5536,6 +6451,11 @@
           <t>The technical skills are often insufficient for the level of difficulty.</t>
         </is>
       </c>
+      <c r="F184" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="27" customHeight="1">
       <c r="A185" s="2" t="inlineStr">
@@ -5563,6 +6483,11 @@
           <t>The technical skills are partially sufficient for the level of difficulty, with recurring uncertainties.</t>
         </is>
       </c>
+      <c r="F185" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="27" customHeight="1">
       <c r="A186" s="2" t="inlineStr">
@@ -5590,6 +6515,11 @@
           <t>The technical skills are largely appropriate to the level of difficulty; isolated uncertainties are noticeable.</t>
         </is>
       </c>
+      <c r="F186" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="27" customHeight="1">
       <c r="A187" s="2" t="inlineStr">
@@ -5617,6 +6547,11 @@
           <t>The technical skills are consistently appropriate to the level of difficulty and performed with confidence.</t>
         </is>
       </c>
+      <c r="F187" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="27" customHeight="1">
       <c r="A188" s="2" t="inlineStr">
@@ -5636,12 +6571,17 @@
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Sicherheit der technischen Fertigkeiten** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Sicherheit der technischen Fertigkeiten bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the security of the technical skills for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the security of the technical skills for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F188" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -5671,6 +6611,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F189" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -5698,6 +6643,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F190" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -5725,6 +6675,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F191" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -5752,6 +6707,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F192" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -5779,6 +6739,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F193" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="27" customHeight="1">
       <c r="A194" s="2" t="inlineStr">
@@ -5798,12 +6763,17 @@
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Sicherheit der technischen Fertigkeiten** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Sicherheit der technischen Fertigkeiten bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the security of the technical skills for this pupil is:</t>
+          <t>**Compared to the last lesson**, the security of the technical skills for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F194" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -5833,6 +6803,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F195" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -5860,6 +6835,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F196" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -5887,6 +6867,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F197" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -5914,6 +6899,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F198" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -5941,8 +6931,13 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
-    </row>
-    <row r="200">
+      <c r="F199" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="27" customHeight="1">
       <c r="A200" s="2" t="inlineStr">
         <is>
           <t>MLP_0012_L3_PROMPT</t>
@@ -5960,15 +6955,20 @@
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel** des/der Schüler/in zu?</t>
+          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel auf dem Holzblasinstrument** des/der Schüler/in zu?</t>
         </is>
       </c>
       <c r="E200" s="4" t="inlineStr">
         <is>
-          <t>Which of these statements applies to the execution of the pupil?</t>
-        </is>
-      </c>
-      <c r="F200" s="7" t="inlineStr">
+          <t>Which of these statements applies to **the woodwind-specific execution** of the pupil?</t>
+        </is>
+      </c>
+      <c r="F200" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G200" s="7" t="inlineStr">
         <is>
           <t>Wesolowski et al. (2017) – Air support ("sufficiency of air", "air support in various registers")</t>
         </is>
@@ -6000,6 +7000,11 @@
           <t>The breathing technique is predominantly uneconomical. Tone production and intonation are consistently unstable.</t>
         </is>
       </c>
+      <c r="F201" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="27" customHeight="1">
       <c r="A202" s="2" t="inlineStr">
@@ -6027,6 +7032,11 @@
           <t>The breathing technique is often uneconomical. Tone production and intonation are correspondingly unstable.</t>
         </is>
       </c>
+      <c r="F202" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="27" customHeight="1">
       <c r="A203" s="2" t="inlineStr">
@@ -6054,6 +7064,11 @@
           <t>The breathing technique is partially economical. Tone production and intonation fluctuate recurringly.</t>
         </is>
       </c>
+      <c r="F203" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="27" customHeight="1">
       <c r="A204" s="2" t="inlineStr">
@@ -6081,6 +7096,11 @@
           <t>The breathing technique is largely economical. Tone production and intonation remain mostly stable, with isolated minor fluctuations.</t>
         </is>
       </c>
+      <c r="F204" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="27" customHeight="1">
       <c r="A205" s="2" t="inlineStr">
@@ -6108,6 +7128,11 @@
           <t>The breathing technique is consistently economical and enables even tone production and stable intonation.</t>
         </is>
       </c>
+      <c r="F205" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="27" customHeight="1">
       <c r="A206" s="2" t="inlineStr">
@@ -6127,12 +7152,17 @@
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Ökonomie der Atemführung** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Ökonomie der Atemführung bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the economy of the breathing technique for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the economy of the breathing technique for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F206" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -6162,6 +7192,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F207" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -6189,6 +7224,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F208" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -6216,6 +7256,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F209" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -6243,6 +7288,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F210" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -6270,6 +7320,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F211" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="27" customHeight="1">
       <c r="A212" s="2" t="inlineStr">
@@ -6289,12 +7344,17 @@
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Ökonomie der Atemführung** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Ökonomie der Atemführung bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E212" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the economy of the breathing technique for this pupil is:</t>
+          <t>**Compared to the last lesson**, the economy of the breathing technique for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F212" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -6324,6 +7384,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F213" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -6351,6 +7416,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F214" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -6378,6 +7448,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F215" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -6405,6 +7480,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F216" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -6432,8 +7512,13 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
-    </row>
-    <row r="218">
+      <c r="F217" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="27" customHeight="1">
       <c r="A218" s="2" t="inlineStr">
         <is>
           <t>MLP_0013_L3_PROMPT</t>
@@ -6451,15 +7536,20 @@
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel** des/der Schüler/in zu?</t>
+          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel auf dem Holzblasinstrument** des/der Schüler/in zu?</t>
         </is>
       </c>
       <c r="E218" s="4" t="inlineStr">
         <is>
-          <t>Which of the following statements applies to the pupil’s instrumental playing?</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
+          <t>Which of these statements applies to **the woodwind-specific execution** of the pupil?</t>
+        </is>
+      </c>
+      <c r="F218" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
         <is>
           <t>Wrigley &amp; Emmerson (2013) – PERS Woodwind ("reed intonation: accurate, control")</t>
         </is>
@@ -6491,6 +7581,11 @@
           <t>The reed/mouthpiece are predominantly used without control; a distinctive, focused tone hardly emerges.</t>
         </is>
       </c>
+      <c r="F219" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="27" customHeight="1">
       <c r="A220" s="2" t="inlineStr">
@@ -6518,6 +7613,11 @@
           <t>The reed/mouthpiece are often used without control; the tone seems correspondingly unfocused.</t>
         </is>
       </c>
+      <c r="F220" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="27" customHeight="1">
       <c r="A221" s="2" t="inlineStr">
@@ -6545,6 +7645,11 @@
           <t>The reed/mouthpiece are partially used with control; the tone is only occasionally focused and distinctive.</t>
         </is>
       </c>
+      <c r="F221" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="27" customHeight="1">
       <c r="A222" s="2" t="inlineStr">
@@ -6572,6 +7677,11 @@
           <t>The reed/mouthpiece are largely used with control; the tone is mostly focused, with isolated deviations.</t>
         </is>
       </c>
+      <c r="F222" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="27" customHeight="1">
       <c r="A223" s="2" t="inlineStr">
@@ -6599,6 +7709,11 @@
           <t>The reed/mouthpiece are consistently used with control and produce a distinctive, focused tone.</t>
         </is>
       </c>
+      <c r="F223" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="27" customHeight="1">
       <c r="A224" s="2" t="inlineStr">
@@ -6618,12 +7733,17 @@
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Kontrolle beim Einsatz von Rohrblatt bzw. Mundstück** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Kontrolle beim Einsatz von Rohrblatt bzw. Mundstück bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E224" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the control in the use of the reed/mouthpiece for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the control in the use of the reed/mouthpiece for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F224" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -6653,6 +7773,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F225" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -6680,6 +7805,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F226" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -6707,6 +7837,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F227" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -6734,6 +7869,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F228" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -6761,6 +7901,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F229" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="27" customHeight="1">
       <c r="A230" s="2" t="inlineStr">
@@ -6780,12 +7925,17 @@
       </c>
       <c r="D230" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Kontrolle beim Einsatz von Rohrblatt bzw. Mundstück** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Kontrolle beim Einsatz von Rohrblatt bzw. Mundstück bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E230" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the control in the use of the reed/mouthpiece for this pupil is:</t>
+          <t>**Compared to the last lesson**, the control in the use of the reed/mouthpiece for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F230" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -6815,6 +7965,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F231" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -6842,6 +7997,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F232" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -6869,6 +8029,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F233" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -6896,6 +8061,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F234" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -6923,8 +8093,13 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
-    </row>
-    <row r="236">
+      <c r="F235" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="27" customHeight="1">
       <c r="A236" s="2" t="inlineStr">
         <is>
           <t>MLP_0014_L3_PROMPT</t>
@@ -6942,15 +8117,20 @@
       </c>
       <c r="D236" s="4" t="inlineStr">
         <is>
-          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel** des/der Schüler/in zu?</t>
+          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel auf dem Holzblasinstrument** des/der Schüler/in zu?</t>
         </is>
       </c>
       <c r="E236" s="4" t="inlineStr">
         <is>
-          <t>Which of the following statements applies to the pupil’s instrumental playing?</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr">
+          <t>Which of these statements applies to **the woodwind-specific execution** of the pupil?</t>
+        </is>
+      </c>
+      <c r="F236" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
         <is>
           <t>Wesolowski et al. (2017) – Articulation ("consistency of articulation")</t>
         </is>
@@ -6982,6 +8162,11 @@
           <t>The initial notes and tongue strikes are predominantly unclean. Background noises are consistently present.</t>
         </is>
       </c>
+      <c r="F237" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="238" ht="27" customHeight="1">
       <c r="A238" s="2" t="inlineStr">
@@ -7009,6 +8194,11 @@
           <t>The initial notes and tongue strikes are often unclean. Background noises occur repeatedly.</t>
         </is>
       </c>
+      <c r="F238" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="27" customHeight="1">
       <c r="A239" s="2" t="inlineStr">
@@ -7036,6 +8226,11 @@
           <t>The initial notes and tongue strikes are partially clear. Recurring background noises are noticeable.</t>
         </is>
       </c>
+      <c r="F239" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="240" ht="27" customHeight="1">
       <c r="A240" s="2" t="inlineStr">
@@ -7063,6 +8258,11 @@
           <t>The initial notes and tongue strikes are largely clear and clean. Isolated, unobtrusive background noises occur.</t>
         </is>
       </c>
+      <c r="F240" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="241" ht="27" customHeight="1">
       <c r="A241" s="2" t="inlineStr">
@@ -7090,6 +8290,11 @@
           <t>The initial notes and tongue strikes are consistently clear and clean. There are no distracting background noises.</t>
         </is>
       </c>
+      <c r="F241" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="27" customHeight="1">
       <c r="A242" s="2" t="inlineStr">
@@ -7109,12 +8314,17 @@
       </c>
       <c r="D242" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Klarheit von Anblastönen und Zungenanschlägen** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Klarheit von Anblastönen und Zungenanschlägen bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E242" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the clarity of the initial notes and tongue strikes for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the clarity of the initial notes and tongue strikes for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F242" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -7144,6 +8354,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F243" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -7171,6 +8386,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F244" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -7198,6 +8418,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F245" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -7225,6 +8450,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F246" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -7252,6 +8482,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F247" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="248" ht="27" customHeight="1">
       <c r="A248" s="2" t="inlineStr">
@@ -7271,12 +8506,17 @@
       </c>
       <c r="D248" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Klarheit von Anblastönen und Zungenanschlägen** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Klarheit von Anblastönen und Zungenanschlägen bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E248" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the clarity of the initial notes and tongue strikes for this pupil is:</t>
+          <t>**Compared to the last lesson**, the clarity of the initial notes and tongue strikes for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F248" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -7306,6 +8546,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F249" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -7333,6 +8578,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F250" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -7360,6 +8610,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F251" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -7387,6 +8642,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F252" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -7414,8 +8674,13 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
-    </row>
-    <row r="254">
+      <c r="F253" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="27" customHeight="1">
       <c r="A254" s="2" t="inlineStr">
         <is>
           <t>MLP_0015_L3_PROMPT</t>
@@ -7433,15 +8698,20 @@
       </c>
       <c r="D254" s="4" t="inlineStr">
         <is>
-          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel** des/der Schüler/in zu?</t>
+          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel auf dem Holzblasinstrument** des/der Schüler/in zu?</t>
         </is>
       </c>
       <c r="E254" s="4" t="inlineStr">
         <is>
-          <t>Which of the following statements applies to the pupil’s instrumental playing?</t>
-        </is>
-      </c>
-      <c r="F254" t="inlineStr">
+          <t>Which of these statements applies to **the woodwind-specific execution** of the pupil?</t>
+        </is>
+      </c>
+      <c r="F254" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
         <is>
           <t>Wesolowski et al. (2017) – Technique ("finger/slide dexterity", "coordination between tongue and fingers/slide")</t>
         </is>
@@ -7473,6 +8743,11 @@
           <t xml:space="preserve">Finger changes are predominantly imprecise and audible. fingering combinations are not performed with confidence.  </t>
         </is>
       </c>
+      <c r="F255" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="27" customHeight="1">
       <c r="A256" s="2" t="inlineStr">
@@ -7500,6 +8775,11 @@
           <t>Finger changes are often imprecise or audible. Fingering combinations are rarely performed with confidence.</t>
         </is>
       </c>
+      <c r="F256" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="27" customHeight="1">
       <c r="A257" s="2" t="inlineStr">
@@ -7527,6 +8807,11 @@
           <t>Finger changes are partially precise. Fingering combinations are only partially performed with confidence.</t>
         </is>
       </c>
+      <c r="F257" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="27" customHeight="1">
       <c r="A258" s="2" t="inlineStr">
@@ -7554,6 +8839,11 @@
           <t>Finger changes are largely precise and silent. Individual fingering combinations still seem uncertain.</t>
         </is>
       </c>
+      <c r="F258" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="27" customHeight="1">
       <c r="A259" s="2" t="inlineStr">
@@ -7581,6 +8871,11 @@
           <t>Finger changes are consistently precise and silent. Fingering combinations are performed with confidence.</t>
         </is>
       </c>
+      <c r="F259" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="27" customHeight="1">
       <c r="A260" s="2" t="inlineStr">
@@ -7600,12 +8895,17 @@
       </c>
       <c r="D260" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Präzision des Fingerwechsels und der Griffkombinationen** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Präzision des Fingerwechsels und der Griffkombinationen bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E260" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the precision of finger changes and fingering combinations for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the precision of finger changes and fingering combinations for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F260" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -7635,6 +8935,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F261" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -7662,6 +8967,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F262" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -7689,6 +8999,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F263" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -7716,6 +9031,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F264" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -7743,6 +9063,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F265" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="266" ht="27" customHeight="1">
       <c r="A266" s="2" t="inlineStr">
@@ -7762,12 +9087,17 @@
       </c>
       <c r="D266" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Präzision des Fingerwechsels und der Griffkombinationen** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Präzision des Fingerwechsels und der Griffkombinationen bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E266" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the precision of finger changes and fingering combinations for this pupil is:</t>
+          <t>**Compared to the last lesson**, the precision of finger changes and fingering combinations for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F266" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -7797,6 +9127,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F267" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -7824,6 +9159,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F268" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -7851,6 +9191,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F269" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -7878,6 +9223,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F270" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -7905,8 +9255,13 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
-    </row>
-    <row r="272">
+      <c r="F271" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="27" customHeight="1">
       <c r="A272" s="2" t="inlineStr">
         <is>
           <t>MLP_0016_L3_PROMPT</t>
@@ -7924,15 +9279,20 @@
       </c>
       <c r="D272" s="4" t="inlineStr">
         <is>
-          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel** des/der Schüler/in zu?</t>
+          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel auf dem Holzblasinstrument** des/der Schüler/in zu?</t>
         </is>
       </c>
       <c r="E272" s="4" t="inlineStr">
         <is>
-          <t>Which of the following statements applies to the pupil’s instrumental playing?</t>
-        </is>
-      </c>
-      <c r="F272" t="inlineStr">
+          <t>Which of these statements applies to **the woodwind-specific execution** of the pupil?</t>
+        </is>
+      </c>
+      <c r="F272" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
         <is>
           <t>Wesolowski et al. (2017) – Intonation + Tone ("tone quality in varying registers")</t>
         </is>
@@ -7964,6 +9324,11 @@
           <t>Intonation and timbre are consistently unstable, regardless of the register.</t>
         </is>
       </c>
+      <c r="F273" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="274" ht="27" customHeight="1">
       <c r="A274" s="2" t="inlineStr">
@@ -7991,6 +9356,11 @@
           <t>Intonation and timbre frequently fluctuate, especially in the outer and overblow registers.</t>
         </is>
       </c>
+      <c r="F274" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="275" ht="27" customHeight="1">
       <c r="A275" s="2" t="inlineStr">
@@ -8018,6 +9388,11 @@
           <t>Intonation and timbre remain stable in the middle register but fluctuate noticeably in overblow registers.</t>
         </is>
       </c>
+      <c r="F275" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="276" ht="27" customHeight="1">
       <c r="A276" s="2" t="inlineStr">
@@ -8045,6 +9420,11 @@
           <t>Intonation and timbre largely remain stable. Isolated minor fluctuations occur in the overblow register.</t>
         </is>
       </c>
+      <c r="F276" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="277" ht="27" customHeight="1">
       <c r="A277" s="2" t="inlineStr">
@@ -8072,6 +9452,11 @@
           <t>Intonation and timbre consistently remain even and stable across all registers – including overblow registers.</t>
         </is>
       </c>
+      <c r="F277" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="278" ht="27" customHeight="1">
       <c r="A278" s="2" t="inlineStr">
@@ -8091,12 +9476,17 @@
       </c>
       <c r="D278" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Stabilität von Intonation und Klangfarbe über alle Lagen** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Stabilität von Intonation und Klangfarbe über alle Lagen bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E278" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the stability of intonation and timbre across all registers for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the stability of intonation and timbre across all registers for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F278" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -8126,6 +9516,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F279" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -8153,6 +9548,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F280" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
@@ -8180,6 +9580,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F281" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -8207,6 +9612,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F282" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -8234,6 +9644,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F283" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="284" ht="27" customHeight="1">
       <c r="A284" s="2" t="inlineStr">
@@ -8253,12 +9668,17 @@
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Stabilität von Intonation und Klangfarbe über alle Lagen** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Stabilität von Intonation und Klangfarbe über alle Lagen bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E284" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the stability of intonation and timbre across all registers for this pupil is:</t>
+          <t>**Compared to the last lesson**, the stability of intonation and timbre across all registers for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F284" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -8288,6 +9708,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F285" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -8315,6 +9740,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F286" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
@@ -8342,6 +9772,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F287" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -8369,6 +9804,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F288" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
@@ -8396,8 +9836,13 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
-    </row>
-    <row r="290">
+      <c r="F289" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="27" customHeight="1">
       <c r="A290" s="2" t="inlineStr">
         <is>
           <t>MLP_0017_L3_PROMPT</t>
@@ -8415,15 +9860,20 @@
       </c>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel** des/der Schüler/in zu?</t>
+          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel auf dem Holzblasinstrument** des/der Schüler/in zu?</t>
         </is>
       </c>
       <c r="E290" s="4" t="inlineStr">
         <is>
-          <t>Which of the following statements applies to the pupil’s instrumental playing?</t>
-        </is>
-      </c>
-      <c r="F290" t="inlineStr">
+          <t>Which of these statements applies to **the woodwind-specific execution** of the pupil?</t>
+        </is>
+      </c>
+      <c r="F290" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
         <is>
           <t>Saunders &amp; Holahan (1997) – Tone (analog zu 0010, hier holzblasspezifisch)</t>
         </is>
@@ -8455,6 +9905,11 @@
           <t>The sound is predominantly thin and lacking resonance. Distracting background noise is consistently present.</t>
         </is>
       </c>
+      <c r="F291" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="292" ht="27" customHeight="1">
       <c r="A292" s="2" t="inlineStr">
@@ -8482,6 +9937,11 @@
           <t>The sound is often thin or lacks resonance;. Background noise occurs repeatedly.</t>
         </is>
       </c>
+      <c r="F292" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="293" ht="27" customHeight="1">
       <c r="A293" s="2" t="inlineStr">
@@ -8509,6 +9969,11 @@
           <t>The sound is partially full and resonant. Recurring background noise (e.g. buzzing) is noticeable.</t>
         </is>
       </c>
+      <c r="F293" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="294" ht="27" customHeight="1">
       <c r="A294" s="2" t="inlineStr">
@@ -8536,6 +10001,11 @@
           <t>The sound is largely full and resonant. Isolated slight background noise occurs.</t>
         </is>
       </c>
+      <c r="F294" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="295" ht="27" customHeight="1">
       <c r="A295" s="2" t="inlineStr">
@@ -8563,6 +10033,11 @@
           <t>The sound is consistently full, resonant and free from distracting background noise (e.g. buzzing).</t>
         </is>
       </c>
+      <c r="F295" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="296" ht="27" customHeight="1">
       <c r="A296" s="2" t="inlineStr">
@@ -8582,12 +10057,17 @@
       </c>
       <c r="D296" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Fülle und Resonanz des Tons** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Fülle und Resonanz des Tons bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E296" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the fullness and resonance of the tone for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the fullness and resonance of the tone for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F296" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -8617,6 +10097,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F297" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -8644,6 +10129,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F298" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
@@ -8671,6 +10161,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F299" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -8698,6 +10193,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F300" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
@@ -8725,6 +10225,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F301" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="302" ht="27" customHeight="1">
       <c r="A302" s="2" t="inlineStr">
@@ -8744,12 +10249,17 @@
       </c>
       <c r="D302" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Fülle und Resonanz des Tons** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Fülle und Resonanz des Tons bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E302" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the fullness and resonance of the tone for this pupil is:</t>
+          <t>**Compared to the last lesson**, the fullness and resonance of the tone for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F302" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -8779,6 +10289,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F303" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -8806,6 +10321,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F304" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
@@ -8833,6 +10353,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F305" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -8860,6 +10385,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F306" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
@@ -8887,8 +10417,13 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
-    </row>
-    <row r="308">
+      <c r="F307" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="27" customHeight="1">
       <c r="A308" s="2" t="inlineStr">
         <is>
           <t>MLP_0018_L3_PROMPT</t>
@@ -8906,15 +10441,20 @@
       </c>
       <c r="D308" s="4" t="inlineStr">
         <is>
-          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel** des/der Schüler/in zu?</t>
+          <t>Welche dieser Aussagen trifft auf **das Spiel auf der Gitarre** des/der Schüler/in zu?</t>
         </is>
       </c>
       <c r="E308" s="4" t="inlineStr">
         <is>
-          <t>Which of the following statements applies to the pupil’s instrumental playing?</t>
-        </is>
-      </c>
-      <c r="F308" t="inlineStr">
+          <t>Which of the following statements applies to **the guitar-specific** instrumental playing of the pupil?</t>
+        </is>
+      </c>
+      <c r="F308" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
         <is>
           <t>Russell (2010a) – GPRS Technique ("poor synchronization of pick and fret-hand fingers")</t>
         </is>
@@ -8946,6 +10486,11 @@
           <t>The right-hand technique is predominantly uncoordinated and tense.</t>
         </is>
       </c>
+      <c r="F309" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -8973,6 +10518,11 @@
           <t>The right-hand technique is often uncoordinated or tense.</t>
         </is>
       </c>
+      <c r="F310" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="311" ht="27" customHeight="1">
       <c r="A311" s="2" t="inlineStr">
@@ -9000,6 +10550,11 @@
           <t>The right-hand technique is partially coordinated; recurring tension or irregularities occur.</t>
         </is>
       </c>
+      <c r="F311" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="312" ht="27" customHeight="1">
       <c r="A312" s="2" t="inlineStr">
@@ -9027,6 +10582,11 @@
           <t>The right-hand technique is largely coordinated and relaxed; isolated tension is noticeable.</t>
         </is>
       </c>
+      <c r="F312" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="313" ht="40.5" customHeight="1">
       <c r="A313" s="2" t="inlineStr">
@@ -9054,6 +10614,11 @@
           <t>The right-hand technique (finger changes i-m, resting stroke/free stroke, thumb bass line) is consistently coordinated and relaxed.</t>
         </is>
       </c>
+      <c r="F313" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="314" ht="27" customHeight="1">
       <c r="A314" s="2" t="inlineStr">
@@ -9073,12 +10638,17 @@
       </c>
       <c r="D314" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Koordination der Anschlagstechnik der rechten Hand** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Koordination der Anschlagstechnik der rechten Hand bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E314" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the coordination of the right-hand technique for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the coordination of the right-hand technique for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F314" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -9108,6 +10678,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F315" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -9135,6 +10710,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F316" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
@@ -9162,6 +10742,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F317" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -9189,6 +10774,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F318" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -9216,6 +10806,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F319" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="320" ht="27" customHeight="1">
       <c r="A320" s="2" t="inlineStr">
@@ -9235,12 +10830,17 @@
       </c>
       <c r="D320" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Koordination der Anschlagstechnik der rechten Hand** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Koordination der Anschlagstechnik der rechten Hand bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E320" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the coordination of the right-hand technique for this pupil is:</t>
+          <t>**Compared to the last lesson**, the coordination of the right-hand technique for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F320" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -9270,6 +10870,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F321" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -9297,6 +10902,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F322" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
@@ -9324,6 +10934,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F323" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -9351,6 +10966,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F324" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
@@ -9378,8 +10998,13 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
-    </row>
-    <row r="326">
+      <c r="F325" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="27" customHeight="1">
       <c r="A326" s="2" t="inlineStr">
         <is>
           <t>MLP_0019_L3_PROMPT</t>
@@ -9397,15 +11022,20 @@
       </c>
       <c r="D326" s="4" t="inlineStr">
         <is>
-          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel** des/der Schüler/in zu?</t>
+          <t>Welche dieser Aussagen trifft auf **das Spiel auf der Gitarre** des/der Schüler/in zu?</t>
         </is>
       </c>
       <c r="E326" s="4" t="inlineStr">
         <is>
-          <t>Which of the following statements applies to the pupil’s instrumental playing?</t>
-        </is>
-      </c>
-      <c r="F326" t="inlineStr">
+          <t>Which of the following statements applies to **the guitar-specific** instrumental playing of the pupil?</t>
+        </is>
+      </c>
+      <c r="F326" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
         <is>
           <t>Russell (2010a) – GPRS Technique ("string crossing is controlled and smooth")</t>
         </is>
@@ -9437,6 +11067,11 @@
           <t>Finger position changes and fingerwork are predominantly unclean and audible.</t>
         </is>
       </c>
+      <c r="F327" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -9464,6 +11099,11 @@
           <t>Finger position changes and fingerwork are often unclean or audible.</t>
         </is>
       </c>
+      <c r="F328" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="329" ht="27" customHeight="1">
       <c r="A329" s="2" t="inlineStr">
@@ -9491,6 +11131,11 @@
           <t>Finger position changes and fingerwork are partially performed cleanly;. Recurring noise or uncertainty is noticeable.</t>
         </is>
       </c>
+      <c r="F329" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="330" ht="27" customHeight="1">
       <c r="A330" s="2" t="inlineStr">
@@ -9518,6 +11163,11 @@
           <t>Finger position changes and fingerwork are largely performed cleanly. Isolated minor noise occurs.</t>
         </is>
       </c>
+      <c r="F330" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="331" ht="27" customHeight="1">
       <c r="A331" s="2" t="inlineStr">
@@ -9545,6 +11195,11 @@
           <t>Finger position changes and fingerwork are consistently performed cleanly and silently.</t>
         </is>
       </c>
+      <c r="F331" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="332" ht="27" customHeight="1">
       <c r="A332" s="2" t="inlineStr">
@@ -9564,12 +11219,17 @@
       </c>
       <c r="D332" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Sauberkeit von Griffwechsel und Lagenspiel** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Sauberkeit von Griffwechsel und Lagenspiel bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E332" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the cleanliness of finger position changes and fingerwork for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the cleanliness of finger position changes and fingerwork for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F332" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -9599,6 +11259,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F333" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -9626,6 +11291,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F334" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
@@ -9653,6 +11323,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F335" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -9680,6 +11355,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F336" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
@@ -9707,6 +11387,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F337" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="338" ht="27" customHeight="1">
       <c r="A338" s="2" t="inlineStr">
@@ -9726,12 +11411,17 @@
       </c>
       <c r="D338" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Sauberkeit von Griffwechsel und Lagenspiel** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Sauberkeit von Griffwechsel und Lagenspiel bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E338" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the cleanliness of finger position changes and fingerwork for this pupil is:</t>
+          <t>**Compared to the last lesson**, the cleanliness of finger position changes and fingerwork for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F338" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -9761,6 +11451,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F339" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
@@ -9788,6 +11483,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F340" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
@@ -9815,6 +11515,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F341" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
@@ -9842,6 +11547,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F342" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
@@ -9869,8 +11579,13 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
-    </row>
-    <row r="344">
+      <c r="F343" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="27" customHeight="1">
       <c r="A344" s="2" t="inlineStr">
         <is>
           <t>MLP_0020_L3_PROMPT</t>
@@ -9888,15 +11603,20 @@
       </c>
       <c r="D344" s="4" t="inlineStr">
         <is>
-          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel** des/der Schüler/in zu?</t>
+          <t>Welche dieser Aussagen trifft auf **das Spiel auf der Gitarre** des/der Schüler/in zu?</t>
         </is>
       </c>
       <c r="E344" s="4" t="inlineStr">
         <is>
-          <t>Which of the following statements applies to the pupil’s instrumental playing?</t>
-        </is>
-      </c>
-      <c r="F344" s="8" t="inlineStr">
+          <t>Which of the following statements applies to **the guitar-specific** instrumental playing of the pupil?</t>
+        </is>
+      </c>
+      <c r="F344" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G344" s="8" t="inlineStr">
         <is>
           <t>kein direktes Pendant in Moura et al. – am ehesten Wrigley &amp; Emmerson (2013), PERS Piano ("texture: clear") als Analogie</t>
         </is>
@@ -9928,6 +11648,11 @@
           <t>There is hardly any distinction between the voices. They consistently blend together.</t>
         </is>
       </c>
+      <c r="F345" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -9955,6 +11680,11 @@
           <t>The distinction between the voices is often unclear.</t>
         </is>
       </c>
+      <c r="F346" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="347" ht="27" customHeight="1">
       <c r="A347" s="2" t="inlineStr">
@@ -9982,6 +11712,11 @@
           <t>There is a partial distinction between the voices; it is not consistently clearly recognisable.</t>
         </is>
       </c>
+      <c r="F347" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="348" ht="27" customHeight="1">
       <c r="A348" s="2" t="inlineStr">
@@ -10009,6 +11744,11 @@
           <t>There is largely a good distinction between the voices; in isolated moments the voices blend slightly.</t>
         </is>
       </c>
+      <c r="F348" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="349" ht="27" customHeight="1">
       <c r="A349" s="2" t="inlineStr">
@@ -10036,6 +11776,11 @@
           <t>There is consistently a clear distinction between the voices (e.g. bass vs. treble).</t>
         </is>
       </c>
+      <c r="F349" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="350" ht="27" customHeight="1">
       <c r="A350" s="2" t="inlineStr">
@@ -10055,12 +11800,17 @@
       </c>
       <c r="D350" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Differenzierung zwischen den Stimmen** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Differenzierung zwischen den Stimmen bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E350" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the differentiation between the voices for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the differentiation between the voices for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F350" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -10090,6 +11840,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F351" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
@@ -10117,6 +11872,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F352" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
@@ -10144,6 +11904,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F353" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
@@ -10171,6 +11936,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F354" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
@@ -10198,6 +11968,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F355" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="356" ht="27" customHeight="1">
       <c r="A356" s="2" t="inlineStr">
@@ -10217,12 +11992,17 @@
       </c>
       <c r="D356" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Differenzierung zwischen den Stimmen** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Differenzierung zwischen den Stimmen bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E356" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the differentiation between the voices for this pupil is:</t>
+          <t>**Compared to the last lesson**, the differentiation between the voices for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F356" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -10252,6 +12032,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F357" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
@@ -10279,6 +12064,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F358" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
@@ -10306,6 +12096,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F359" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
@@ -10333,6 +12128,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F360" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
@@ -10360,8 +12160,13 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
-    </row>
-    <row r="362">
+      <c r="F361" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="362" ht="27" customHeight="1">
       <c r="A362" s="2" t="inlineStr">
         <is>
           <t>MLP_0021_L3_PROMPT</t>
@@ -10379,15 +12184,20 @@
       </c>
       <c r="D362" s="4" t="inlineStr">
         <is>
-          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel** des/der Schüler/in zu?</t>
+          <t>Welche dieser Aussagen trifft auf **das Spiel auf der Gitarre** des/der Schüler/in zu?</t>
         </is>
       </c>
       <c r="E362" s="4" t="inlineStr">
         <is>
-          <t>Which of the following statements applies to the pupil’s instrumental playing?</t>
-        </is>
-      </c>
-      <c r="F362" t="inlineStr">
+          <t>Which of the following statements applies to **the guitar-specific** instrumental playing of the pupil?</t>
+        </is>
+      </c>
+      <c r="F362" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
         <is>
           <t>Russell (2010a) – GPRS Technique (allgemeine Technikkategorie, kein separates Item für linke Hand)</t>
         </is>
@@ -10419,6 +12229,11 @@
           <t>The left hand's grip technique is predominantly imprecise and unclean.</t>
         </is>
       </c>
+      <c r="F363" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
@@ -10446,6 +12261,11 @@
           <t>The left hand's grip technique is often imprecise or unclean.</t>
         </is>
       </c>
+      <c r="F364" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="365" ht="27" customHeight="1">
       <c r="A365" s="2" t="inlineStr">
@@ -10473,6 +12293,11 @@
           <t>The left hand's grip technique is partially clean and precise, with recurring inaccuracies.</t>
         </is>
       </c>
+      <c r="F365" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="366" ht="27" customHeight="1">
       <c r="A366" s="2" t="inlineStr">
@@ -10500,6 +12325,11 @@
           <t>The left hand largely has a clean and precise grip technique. Isolated inaccuracies occur.</t>
         </is>
       </c>
+      <c r="F366" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
@@ -10527,6 +12357,11 @@
           <t>The left hand consistently has a clean and precise grip technique.</t>
         </is>
       </c>
+      <c r="F367" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="368" ht="27" customHeight="1">
       <c r="A368" s="2" t="inlineStr">
@@ -10546,12 +12381,17 @@
       </c>
       <c r="D368" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Präzision der Grifftechnik der linken Hand** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Präzision der Grifftechnik der linken Hand bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E368" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the precision of the left-hand grip technique for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the precision of the left-hand grip technique for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F368" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -10581,6 +12421,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F369" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
@@ -10608,6 +12453,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F370" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
@@ -10635,6 +12485,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F371" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
@@ -10662,6 +12517,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F372" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
@@ -10689,6 +12549,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F373" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="374" ht="27" customHeight="1">
       <c r="A374" s="2" t="inlineStr">
@@ -10708,12 +12573,17 @@
       </c>
       <c r="D374" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Präzision der Grifftechnik der linken Hand** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Präzision der Grifftechnik der linken Hand bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E374" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the precision of the left-hand grip technique for this pupil is:</t>
+          <t>**Compared to the last lesson**, the precision of the left-hand grip technique for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F374" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -10743,6 +12613,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F375" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
@@ -10770,6 +12645,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F376" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
@@ -10797,6 +12677,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F377" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
@@ -10824,6 +12709,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F378" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
@@ -10851,8 +12741,13 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
-    </row>
-    <row r="380">
+      <c r="F379" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="380" ht="27" customHeight="1">
       <c r="A380" s="2" t="inlineStr">
         <is>
           <t>MLP_0022_L3_PROMPT</t>
@@ -10870,15 +12765,20 @@
       </c>
       <c r="D380" s="4" t="inlineStr">
         <is>
-          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel** des/der Schüler/in zu?</t>
+          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel auf dem Blechblasinstrument** des/der Schüler/in zu?</t>
         </is>
       </c>
       <c r="E380" s="4" t="inlineStr">
         <is>
-          <t>Which of the following statements applies to the pupil’s instrumental playing?</t>
-        </is>
-      </c>
-      <c r="F380" t="inlineStr">
+          <t>Which of the following statements applies to the pupil’s **brass-specific playing**?</t>
+        </is>
+      </c>
+      <c r="F380" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
         <is>
           <t>Wrigley &amp; Emmerson (2013) – PERS Brass ("airflow/breathing: efficient")</t>
         </is>
@@ -10910,6 +12810,11 @@
           <t>The breath support is predominantly unstable. A controlled sound rarely succeeds.</t>
         </is>
       </c>
+      <c r="F381" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="382" ht="27" customHeight="1">
       <c r="A382" s="2" t="inlineStr">
@@ -10937,6 +12842,11 @@
           <t>The breath support is often unstable. the sound is correspondingly uncontrolled.</t>
         </is>
       </c>
+      <c r="F382" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="383" ht="27" customHeight="1">
       <c r="A383" s="2" t="inlineStr">
@@ -10964,6 +12874,11 @@
           <t>The breath support is partially consistent. The sound is less controlled in individual registers.</t>
         </is>
       </c>
+      <c r="F383" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="384" ht="27" customHeight="1">
       <c r="A384" s="2" t="inlineStr">
@@ -10991,6 +12906,11 @@
           <t>The breath support is largely consistent. The sound is controlled in most registers, with isolated fluctuations.</t>
         </is>
       </c>
+      <c r="F384" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="385" ht="27" customHeight="1">
       <c r="A385" s="2" t="inlineStr">
@@ -11018,6 +12938,11 @@
           <t>The breath support is consistently steady and ensures a controlled, sustained sound across all registers.</t>
         </is>
       </c>
+      <c r="F385" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="386" ht="27" customHeight="1">
       <c r="A386" s="2" t="inlineStr">
@@ -11037,12 +12962,17 @@
       </c>
       <c r="D386" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Konstanz der Atemstütze** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Konstanz der Atemstütze bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E386" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the consistency of the breath support for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the consistency of the breath support for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F386" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -11072,6 +13002,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F387" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
@@ -11099,6 +13034,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F388" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
@@ -11126,6 +13066,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F389" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
@@ -11153,6 +13098,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F390" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
@@ -11180,6 +13130,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F391" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="392" ht="27" customHeight="1">
       <c r="A392" s="2" t="inlineStr">
@@ -11199,12 +13154,17 @@
       </c>
       <c r="D392" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Konstanz der Atemstütze** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Konstanz der Atemstütze bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E392" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the consistency of the breath support for this pupil is:</t>
+          <t>**Compared to the last lesson**, the consistency of the breath support for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F392" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -11234,6 +13194,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F393" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
@@ -11261,6 +13226,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F394" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
@@ -11288,6 +13258,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F395" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
@@ -11315,6 +13290,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F396" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
@@ -11342,8 +13322,13 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
-    </row>
-    <row r="398">
+      <c r="F397" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="398" ht="27" customHeight="1">
       <c r="A398" s="2" t="inlineStr">
         <is>
           <t>MLP_0023_L3_PROMPT</t>
@@ -11361,15 +13346,20 @@
       </c>
       <c r="D398" s="4" t="inlineStr">
         <is>
-          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel** des/der Schüler/in zu?</t>
+          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel auf dem Blechblasinstrument** des/der Schüler/in zu?</t>
         </is>
       </c>
       <c r="E398" s="4" t="inlineStr">
         <is>
-          <t>Which of the following statements applies to the pupil’s instrumental playing?</t>
-        </is>
-      </c>
-      <c r="F398" t="inlineStr">
+          <t>Which of the following statements applies to the pupil’s **brass-specific playing**?</t>
+        </is>
+      </c>
+      <c r="F398" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
         <is>
           <t>Wrigley &amp; Emmerson (2013) – PERS Brass ("tone/sound: clear"); Bergee (1993) – BPRS Tone quality/intonation</t>
         </is>
@@ -11401,6 +13391,11 @@
           <t>The embouchure is predominantly unstable. Consistent sound production rarely succeeds.</t>
         </is>
       </c>
+      <c r="F399" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="400" ht="27" customHeight="1">
       <c r="A400" s="2" t="inlineStr">
@@ -11428,6 +13423,11 @@
           <t>The embouchure is often unstable. Sound production is correspondingly uneven.</t>
         </is>
       </c>
+      <c r="F400" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="401" ht="27" customHeight="1">
       <c r="A401" s="2" t="inlineStr">
@@ -11455,6 +13455,11 @@
           <t>The embouchure is partially stable. Sound production fluctuates noticeably in parts of the range.</t>
         </is>
       </c>
+      <c r="F401" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="402" ht="27" customHeight="1">
       <c r="A402" s="2" t="inlineStr">
@@ -11482,6 +13487,11 @@
           <t>The embouchure is largely stable. Sound production is even across most of the range.</t>
         </is>
       </c>
+      <c r="F402" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="403" ht="27" customHeight="1">
       <c r="A403" s="2" t="inlineStr">
@@ -11509,6 +13519,11 @@
           <t>The embouchure is consistently stable and ensures consistent sound production across the entire range.</t>
         </is>
       </c>
+      <c r="F403" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="404" ht="27" customHeight="1">
       <c r="A404" s="2" t="inlineStr">
@@ -11528,12 +13543,17 @@
       </c>
       <c r="D404" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Stabilität des Ansatzes** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Stabilität des Ansatzes bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E404" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the stability of the embouchure for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the stability of the embouchure for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F404" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -11563,6 +13583,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F405" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
@@ -11590,6 +13615,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F406" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
@@ -11617,6 +13647,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F407" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
@@ -11644,6 +13679,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F408" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
@@ -11671,6 +13711,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F409" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="410" ht="27" customHeight="1">
       <c r="A410" s="2" t="inlineStr">
@@ -11690,12 +13735,17 @@
       </c>
       <c r="D410" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Stabilität des Ansatzes** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Stabilität des Ansatzes bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E410" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the stability of the embouchure for this pupil is:</t>
+          <t>**Compared to the last lesson**, the stability of the embouchure for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F410" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -11725,6 +13775,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F411" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
@@ -11752,6 +13807,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F412" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
@@ -11779,6 +13839,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F413" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
@@ -11806,6 +13871,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F414" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
@@ -11833,8 +13903,13 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
-    </row>
-    <row r="416">
+      <c r="F415" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="416" ht="27" customHeight="1">
       <c r="A416" s="2" t="inlineStr">
         <is>
           <t>MLP_0024_L3_PROMPT</t>
@@ -11852,15 +13927,20 @@
       </c>
       <c r="D416" s="4" t="inlineStr">
         <is>
-          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel** des/der Schüler/in zu?</t>
+          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel auf dem Blechblasinstrument** des/der Schüler/in zu?</t>
         </is>
       </c>
       <c r="E416" s="4" t="inlineStr">
         <is>
-          <t>Which of the following statements applies to the pupil’s instrumental playing?</t>
-        </is>
-      </c>
-      <c r="F416" t="inlineStr">
+          <t>Which of the following statements applies to the pupil’s **brass-specific playing**?</t>
+        </is>
+      </c>
+      <c r="F416" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
         <is>
           <t>Bergee (1993) – BPRS Technique ("poor synchronization of tongue and fingers (slide)")</t>
         </is>
@@ -11892,6 +13972,11 @@
           <t>Tongue articulation and finger/slide movements are predominantly unsynchronised.</t>
         </is>
       </c>
+      <c r="F417" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="418" ht="27" customHeight="1">
       <c r="A418" s="2" t="inlineStr">
@@ -11919,6 +14004,11 @@
           <t>Tongue articulation and finger/slide movements are often unsynchronised.</t>
         </is>
       </c>
+      <c r="F418" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="419" ht="27" customHeight="1">
       <c r="A419" s="2" t="inlineStr">
@@ -11946,6 +14036,11 @@
           <t>Tongue articulation and finger/slide movements are partially synchronised, with recurring deviations.</t>
         </is>
       </c>
+      <c r="F419" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="420" ht="27" customHeight="1">
       <c r="A420" s="2" t="inlineStr">
@@ -11973,6 +14068,11 @@
           <t>Tongue articulation and finger/slide movements are largely synchronised;. Isolated minor deviations occur.</t>
         </is>
       </c>
+      <c r="F420" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="421" ht="27" customHeight="1">
       <c r="A421" s="2" t="inlineStr">
@@ -12000,6 +14100,11 @@
           <t>Tongue articulation and finger/slide movements are consistently precisely synchronised.</t>
         </is>
       </c>
+      <c r="F421" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="422" ht="40.5" customHeight="1">
       <c r="A422" s="2" t="inlineStr">
@@ -12019,12 +14124,17 @@
       </c>
       <c r="D422" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Synchronisation von Zungenartikulation und Finger-/Zugbewegungen** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Synchronisation von Zungenartikulation und Finger-/Zugbewegungen bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E422" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the synchronisation of tongue articulation and finger/slide movements for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the synchronisation of tongue articulation and finger/slide movements for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F422" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -12054,6 +14164,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F423" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
@@ -12081,6 +14196,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F424" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
@@ -12108,6 +14228,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F425" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
@@ -12135,6 +14260,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F426" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
@@ -12162,6 +14292,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F427" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="428" ht="27" customHeight="1">
       <c r="A428" s="2" t="inlineStr">
@@ -12181,12 +14316,17 @@
       </c>
       <c r="D428" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Synchronisation von Zungenartikulation und Finger-/Zugbewegungen** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Synchronisation von Zungenartikulation und Finger-/Zugbewegungen bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E428" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the synchronisation of tongue articulation and finger/slide movements for this pupil is:</t>
+          <t>**Compared to the last lesson**, the synchronisation of tongue articulation and finger/slide movements for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F428" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -12216,6 +14356,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F429" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
@@ -12243,6 +14388,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F430" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
@@ -12270,6 +14420,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F431" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
@@ -12297,6 +14452,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F432" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
@@ -12324,8 +14484,13 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
-    </row>
-    <row r="434">
+      <c r="F433" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="434" ht="27" customHeight="1">
       <c r="A434" s="2" t="inlineStr">
         <is>
           <t>MLP_0025_L3_PROMPT</t>
@@ -12343,15 +14508,20 @@
       </c>
       <c r="D434" s="4" t="inlineStr">
         <is>
-          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel** des/der Schüler/in zu?</t>
+          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel auf dem Blechblasinstrument** des/der Schüler/in zu?</t>
         </is>
       </c>
       <c r="E434" s="4" t="inlineStr">
         <is>
-          <t>Which of the following statements applies to the pupil’s instrumental playing?</t>
-        </is>
-      </c>
-      <c r="F434" t="inlineStr">
+          <t>Which of the following statements applies to the pupil’s **brass-specific playing**?</t>
+        </is>
+      </c>
+      <c r="F434" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
         <is>
           <t>Bergee (1993) – BPRS Tone quality/intonation ("sound in upper register is pinched and restricted")</t>
         </is>
@@ -12383,6 +14553,11 @@
           <t>Sound quality and intonation consistently decline noticeably in the upper register and towards the end of the performance.</t>
         </is>
       </c>
+      <c r="F435" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="436" ht="27" customHeight="1">
       <c r="A436" s="2" t="inlineStr">
@@ -12410,6 +14585,11 @@
           <t>Sound quality and intonation often decline noticeably in the upper register or towards the end of the performance.</t>
         </is>
       </c>
+      <c r="F436" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="437" ht="27" customHeight="1">
       <c r="A437" s="2" t="inlineStr">
@@ -12437,6 +14617,11 @@
           <t>Sound quality and intonation partially remain consistent but decline noticeably in the upper register or towards the end.</t>
         </is>
       </c>
+      <c r="F437" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="438" ht="27" customHeight="1">
       <c r="A438" s="2" t="inlineStr">
@@ -12464,6 +14649,11 @@
           <t>Sound quality and intonation largely remain consistent; isolated minor declines occur towards the end or in the upper register.</t>
         </is>
       </c>
+      <c r="F438" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="439" ht="27" customHeight="1">
       <c r="A439" s="2" t="inlineStr">
@@ -12491,6 +14681,11 @@
           <t>Sound quality and intonation consistently remain steady even in the upper register and towards the end of the performance.</t>
         </is>
       </c>
+      <c r="F439" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="440" ht="27" customHeight="1">
       <c r="A440" s="2" t="inlineStr">
@@ -12510,12 +14705,17 @@
       </c>
       <c r="D440" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Konstanz von Klangqualität und Intonation über die Darbietung hinweg** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Konstanz von Klangqualität und Intonation über die Darbietung hinweg bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E440" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the consistency of sound quality and intonation throughout the performance for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the consistency of sound quality and intonation throughout the performance for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F440" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -12545,6 +14745,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F441" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
@@ -12572,6 +14777,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F442" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
@@ -12599,6 +14809,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F443" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
@@ -12626,6 +14841,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F444" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
@@ -12653,6 +14873,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F445" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="446" ht="27" customHeight="1">
       <c r="A446" s="2" t="inlineStr">
@@ -12672,12 +14897,17 @@
       </c>
       <c r="D446" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Konstanz von Klangqualität und Intonation über die Darbietung hinweg** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Konstanz von Klangqualität und Intonation über die Darbietung hinweg bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E446" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the consistency of sound quality and intonation throughout the performance for this pupil is:</t>
+          <t>**Compared to the last lesson**, the consistency of sound quality and intonation throughout the performance for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F446" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -12707,6 +14937,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F447" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
@@ -12734,6 +14969,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F448" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
@@ -12761,6 +15001,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F449" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
@@ -12788,6 +15033,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F450" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
@@ -12815,8 +15065,13 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
-    </row>
-    <row r="452">
+      <c r="F451" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="452" ht="27" customHeight="1">
       <c r="A452" s="2" t="inlineStr">
         <is>
           <t>MLP_0026_L3_PROMPT</t>
@@ -12834,15 +15089,20 @@
       </c>
       <c r="D452" s="4" t="inlineStr">
         <is>
-          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel** des/der Schüler/in zu?</t>
+          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel auf dem Streichinstrument** des/der Schüler/in zu?</t>
         </is>
       </c>
       <c r="E452" s="4" t="inlineStr">
         <is>
-          <t>Which of the following statements applies to the pupil’s instrumental playing?</t>
-        </is>
-      </c>
-      <c r="F452" t="inlineStr">
+          <t>Which of the following statements applies to the pupil’s **strings-specific playing**?</t>
+        </is>
+      </c>
+      <c r="F452" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
         <is>
           <t>Zdzinski &amp; Barnes (2002) – SPRS Articulation/tone ("arm weight draws full sound from string...maintains proper contact point")</t>
         </is>
@@ -12874,6 +15134,11 @@
           <t>The bowing is predominantly uneven. A full, resonant sound rarely emerges.</t>
         </is>
       </c>
+      <c r="F453" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="454" ht="27" customHeight="1">
       <c r="A454" s="2" t="inlineStr">
@@ -12901,6 +15166,11 @@
           <t>The bowing is often uneven. The sound is correspondingly limited in fullness or resonance.</t>
         </is>
       </c>
+      <c r="F454" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="455" ht="27" customHeight="1">
       <c r="A455" s="2" t="inlineStr">
@@ -12928,6 +15198,11 @@
           <t>The bow is partially guided appropriately. Pressure, contact point or speed are recurringly uneven.</t>
         </is>
       </c>
+      <c r="F455" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="456" ht="27" customHeight="1">
       <c r="A456" s="2" t="inlineStr">
@@ -12955,6 +15230,11 @@
           <t>The bow is largely guided appropriately and produces a mostly full sound, with isolated minor irregularities.</t>
         </is>
       </c>
+      <c r="F456" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="457" ht="40.5" customHeight="1">
       <c r="A457" s="2" t="inlineStr">
@@ -12982,6 +15262,11 @@
           <t>The bow is consistently guided with the right amount of pressure, the correct point of contact and varying speed, producing a full, resonant sound.</t>
         </is>
       </c>
+      <c r="F457" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="458" ht="27" customHeight="1">
       <c r="A458" s="2" t="inlineStr">
@@ -13001,12 +15286,17 @@
       </c>
       <c r="D458" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Qualität der Bogenführung** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Qualität der Bogenführung bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E458" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the quality of the bowing for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the quality of the bowing for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F458" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -13036,6 +15326,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F459" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
@@ -13063,6 +15358,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F460" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
@@ -13090,6 +15390,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F461" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
@@ -13117,6 +15422,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F462" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
@@ -13144,6 +15454,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F463" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="464" ht="27" customHeight="1">
       <c r="A464" s="2" t="inlineStr">
@@ -13163,12 +15478,17 @@
       </c>
       <c r="D464" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Qualität der Bogenführung** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Qualität der Bogenführung bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E464" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the quality of the bowing for this pupil is:</t>
+          <t>**Compared to the last lesson**, the quality of the bowing for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F464" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -13198,6 +15518,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F465" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
@@ -13225,6 +15550,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F466" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
@@ -13252,6 +15582,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F467" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
@@ -13279,6 +15614,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F468" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
@@ -13306,8 +15646,13 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
-    </row>
-    <row r="470">
+      <c r="F469" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="470" ht="27" customHeight="1">
       <c r="A470" s="2" t="inlineStr">
         <is>
           <t>MLP_0027_L3_PROMPT</t>
@@ -13325,15 +15670,20 @@
       </c>
       <c r="D470" s="4" t="inlineStr">
         <is>
-          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel** des/der Schüler/in zu?</t>
+          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel auf dem Streichinstrument** des/der Schüler/in zu?</t>
         </is>
       </c>
       <c r="E470" s="4" t="inlineStr">
         <is>
-          <t>Which of the following statements applies to the pupil’s instrumental playing?</t>
-        </is>
-      </c>
-      <c r="F470" t="inlineStr">
+          <t>Which of the following statements applies to the pupil’s **strings-specific playing**?</t>
+        </is>
+      </c>
+      <c r="F470" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
         <is>
           <t>Zdzinski &amp; Barnes (2002) – SPRS Articulation/tone ("string crossings are controlled")</t>
         </is>
@@ -13365,6 +15715,11 @@
           <t>String changes are predominantly associated with audible breaks in the legato.</t>
         </is>
       </c>
+      <c r="F471" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
@@ -13392,6 +15747,11 @@
           <t>String changes are often associated with audible breaks in the legato.</t>
         </is>
       </c>
+      <c r="F472" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="473" ht="27" customHeight="1">
       <c r="A473" s="2" t="inlineStr">
@@ -13419,6 +15779,11 @@
           <t>String changes are partially performed smoothly. Recurring breaks in the legato are audible.</t>
         </is>
       </c>
+      <c r="F473" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="474" ht="27" customHeight="1">
       <c r="A474" s="2" t="inlineStr">
@@ -13446,6 +15811,11 @@
           <t>String changes are largely performed smoothly. Isolated minor breaks are audible.</t>
         </is>
       </c>
+      <c r="F474" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="475" ht="27" customHeight="1">
       <c r="A475" s="2" t="inlineStr">
@@ -13473,6 +15843,11 @@
           <t>String changes are consistently performed smoothly and without any audible breaks in the legato.</t>
         </is>
       </c>
+      <c r="F475" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="476" ht="27" customHeight="1">
       <c r="A476" s="2" t="inlineStr">
@@ -13492,12 +15867,17 @@
       </c>
       <c r="D476" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Fließfähigkeit der Saitenwechsel im Legato** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Fließfähigkeit der Saitenwechsel im Legato bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E476" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the fluency of string changes in legato for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the fluency of string changes in legato for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F476" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -13527,6 +15907,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F477" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
@@ -13554,6 +15939,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F478" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
@@ -13581,6 +15971,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F479" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
@@ -13608,6 +16003,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F480" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
@@ -13635,6 +16035,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F481" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="482" ht="27" customHeight="1">
       <c r="A482" s="2" t="inlineStr">
@@ -13654,12 +16059,17 @@
       </c>
       <c r="D482" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Fließfähigkeit der Saitenwechsel im Legato** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Fließfähigkeit der Saitenwechsel im Legato bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E482" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the fluency of string changes in legato for this pupil is:</t>
+          <t>**Compared to the last lesson**, the fluency of string changes in legato for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F482" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -13689,6 +16099,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F483" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
@@ -13716,6 +16131,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F484" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
@@ -13743,6 +16163,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F485" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
@@ -13770,6 +16195,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F486" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
@@ -13797,8 +16227,13 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
-    </row>
-    <row r="488">
+      <c r="F487" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="488" ht="27" customHeight="1">
       <c r="A488" s="2" t="inlineStr">
         <is>
           <t>MLP_0028_L3_PROMPT</t>
@@ -13816,15 +16251,20 @@
       </c>
       <c r="D488" s="4" t="inlineStr">
         <is>
-          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel** des/der Schüler/in zu?</t>
+          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel auf dem Streichinstrument** des/der Schüler/in zu?</t>
         </is>
       </c>
       <c r="E488" s="4" t="inlineStr">
         <is>
-          <t>Which of the following statements applies to the pupil’s instrumental playing?</t>
-        </is>
-      </c>
-      <c r="F488" t="inlineStr">
+          <t>Which of the following statements applies to the pupil’s **strings-specific playing**?</t>
+        </is>
+      </c>
+      <c r="F488" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
         <is>
           <t>Zdzinski &amp; Barnes (2002) – SPRS Articulation/tone ("clear articulation produced by left hand")</t>
         </is>
@@ -13856,6 +16296,11 @@
           <t>The plucking hand works predominantly uncleanly. Notes are mostly plucked unclearly.</t>
         </is>
       </c>
+      <c r="F489" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
@@ -13883,6 +16328,11 @@
           <t>The plucking hand often works uncleanly. Extraneous noise occurs repeatedly.</t>
         </is>
       </c>
+      <c r="F490" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="491" ht="27" customHeight="1">
       <c r="A491" s="2" t="inlineStr">
@@ -13910,6 +16360,11 @@
           <t>The plucking hand works partially cleanly. Recurring extraneous noise or unclearly plucked notes are noticeable.</t>
         </is>
       </c>
+      <c r="F491" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="492" ht="27" customHeight="1">
       <c r="A492" s="2" t="inlineStr">
@@ -13937,6 +16392,11 @@
           <t>The plucking hand largely works cleanly. Isolated minor extraneous noise occurs.</t>
         </is>
       </c>
+      <c r="F492" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="493" ht="27" customHeight="1">
       <c r="A493" s="2" t="inlineStr">
@@ -13964,6 +16424,11 @@
           <t>The plucking hand consistently works cleanly. Notes are plucked clearly and produced without any extraneous noise.</t>
         </is>
       </c>
+      <c r="F493" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="494" ht="27" customHeight="1">
       <c r="A494" s="2" t="inlineStr">
@@ -13983,12 +16448,17 @@
       </c>
       <c r="D494" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Sauberkeit der Greifhand** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Sauberkeit der Greifhand bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E494" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the cleanliness of the plucking hand for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the cleanliness of the plucking hand for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F494" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -14018,6 +16488,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F495" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
@@ -14045,6 +16520,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F496" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="inlineStr">
@@ -14072,6 +16552,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F497" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
@@ -14099,6 +16584,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F498" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="inlineStr">
@@ -14126,6 +16616,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F499" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="500" ht="27" customHeight="1">
       <c r="A500" s="2" t="inlineStr">
@@ -14145,12 +16640,17 @@
       </c>
       <c r="D500" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Sauberkeit der Greifhand** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Sauberkeit der Greifhand bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E500" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the cleanliness of the plucking hand for this pupil is:</t>
+          <t>**Compared to the last lesson**, the cleanliness of the plucking hand for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F500" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -14180,6 +16680,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F501" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
@@ -14207,6 +16712,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F502" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
@@ -14234,6 +16744,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F503" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
@@ -14261,6 +16776,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F504" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
@@ -14288,8 +16808,13 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
-    </row>
-    <row r="506">
+      <c r="F505" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="506" ht="27" customHeight="1">
       <c r="A506" s="2" t="inlineStr">
         <is>
           <t>MLP_0029_L3_PROMPT</t>
@@ -14307,15 +16832,20 @@
       </c>
       <c r="D506" s="4" t="inlineStr">
         <is>
-          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel** des/der Schüler/in zu?</t>
+          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel auf dem Streichinstrument** des/der Schüler/in zu?</t>
         </is>
       </c>
       <c r="E506" s="4" t="inlineStr">
         <is>
-          <t>Which of the following statements applies to the pupil’s instrumental playing?</t>
-        </is>
-      </c>
-      <c r="F506" t="inlineStr">
+          <t>Which of the following statements applies to the pupil’s **strings-specific playing**?</t>
+        </is>
+      </c>
+      <c r="F506" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
         <is>
           <t>Zdzinski &amp; Barnes (2002) – SPRS Intonation ("half steps not close enough", "performer was able to adjust pitch")</t>
         </is>
@@ -14347,6 +16877,11 @@
           <t>The intonation is predominantly imprecise. Intonation problems are not corrected independently.</t>
         </is>
       </c>
+      <c r="F507" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="508" ht="27.75" customHeight="1">
       <c r="A508" s="2" t="inlineStr">
@@ -14374,6 +16909,11 @@
           <t>The intonation frequently shows inaccuracies. Intonation problems are rarely corrected independently.</t>
         </is>
       </c>
+      <c r="F508" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="509" ht="27.75" customHeight="1">
       <c r="A509" s="2" t="inlineStr">
@@ -14401,6 +16941,11 @@
           <t>The intonation is partially precise. Intonation problems are only partially recognised and corrected independently.</t>
         </is>
       </c>
+      <c r="F509" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="510" ht="27.75" customHeight="1">
       <c r="A510" s="2" t="inlineStr">
@@ -14428,6 +16973,11 @@
           <t>The intonation is largely precise. Isolated deviations are mostly corrected independently.</t>
         </is>
       </c>
+      <c r="F510" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="511" ht="27.75" customHeight="1">
       <c r="A511" s="2" t="inlineStr">
@@ -14455,6 +17005,11 @@
           <t>The intonation is consistently precise. Semitones are spaced closely enough, and intonation problems are corrected independently.</t>
         </is>
       </c>
+      <c r="F511" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="512" ht="27" customHeight="1">
       <c r="A512" s="2" t="inlineStr">
@@ -14474,12 +17029,17 @@
       </c>
       <c r="D512" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Präzision der Intonation und die eigenständige Fehlerkorrektur** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Präzision der Intonation und die eigenständige Fehlerkorrektur bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E512" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the precision of intonation and independent error correction for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the precision of intonation and independent error correction for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F512" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -14509,6 +17069,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F513" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" s="2" t="inlineStr">
@@ -14536,6 +17101,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F514" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" s="2" t="inlineStr">
@@ -14563,6 +17133,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F515" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" s="2" t="inlineStr">
@@ -14590,6 +17165,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F516" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" s="2" t="inlineStr">
@@ -14617,6 +17197,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F517" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="518" ht="27" customHeight="1">
       <c r="A518" s="2" t="inlineStr">
@@ -14636,12 +17221,17 @@
       </c>
       <c r="D518" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Präzision der Intonation und die eigenständige Fehlerkorrektur** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Präzision der Intonation und die eigenständige Fehlerkorrektur bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E518" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the precision of intonation and independent error correction for this pupil is:</t>
+          <t>**Compared to the last lesson**, the precision of intonation and independent error correction for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F518" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -14671,6 +17261,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F519" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" s="2" t="inlineStr">
@@ -14698,6 +17293,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F520" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" s="2" t="inlineStr">
@@ -14725,6 +17325,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F521" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" s="2" t="inlineStr">
@@ -14752,6 +17357,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F522" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" s="2" t="inlineStr">
@@ -14779,8 +17389,13 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
-    </row>
-    <row r="524">
+      <c r="F523" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="524" ht="27" customHeight="1">
       <c r="A524" s="2" t="inlineStr">
         <is>
           <t>MLP_0030_L3_PROMPT</t>
@@ -14798,15 +17413,20 @@
       </c>
       <c r="D524" s="4" t="inlineStr">
         <is>
-          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel** des/der Schüler/in zu?</t>
+          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel auf dem Streichinstrument** des/der Schüler/in zu?</t>
         </is>
       </c>
       <c r="E524" s="4" t="inlineStr">
         <is>
-          <t>Which of the following statements applies to the pupil’s instrumental playing?</t>
-        </is>
-      </c>
-      <c r="F524" t="inlineStr">
+          <t>Which of the following statements applies to the pupil’s **strings-specific playing**?</t>
+        </is>
+      </c>
+      <c r="F524" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
         <is>
           <t>Zdzinski &amp; Barnes (2002) – SPRS Vibrato ("full, rich vibrato", "vibrato is continuous/even")</t>
         </is>
@@ -14838,6 +17458,11 @@
           <t>The vibrato is predominantly uneven or absent. Musically appropriate use is hardly recognisable.</t>
         </is>
       </c>
+      <c r="F525" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="526" ht="27" customHeight="1">
       <c r="A526" s="2" t="inlineStr">
@@ -14865,6 +17490,11 @@
           <t>The vibrato is often uneven or used with little musical justification.</t>
         </is>
       </c>
+      <c r="F526" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="527" ht="27" customHeight="1">
       <c r="A527" s="2" t="inlineStr">
@@ -14892,6 +17522,11 @@
           <t>The vibrato is partially even. Its use does not consistently seem musically justified.</t>
         </is>
       </c>
+      <c r="F527" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="528" ht="27" customHeight="1">
       <c r="A528" s="2" t="inlineStr">
@@ -14919,6 +17554,11 @@
           <t>The vibrato is largely even and expressive. Its use is mostly musically appropriate.</t>
         </is>
       </c>
+      <c r="F528" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="529" ht="27" customHeight="1">
       <c r="A529" s="2" t="inlineStr">
@@ -14946,6 +17586,11 @@
           <t>The vibrato is consistently even and expressive and is used flexibly and in a musically appropriate manner.</t>
         </is>
       </c>
+      <c r="F529" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="530" ht="40.5" customHeight="1">
       <c r="A530" s="2" t="inlineStr">
@@ -14965,12 +17610,17 @@
       </c>
       <c r="D530" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Gleichmäßigkeit und der musikalisch sinnvolle Einsatz des Vibratos** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Gleichmäßigkeit und der musikalisch sinnvolle Einsatz des Vibratos bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E530" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the evenness and musically appropriate use of the vibrato for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the evenness and musically appropriate use of the vibrato for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F530" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -15000,6 +17650,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F531" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" s="2" t="inlineStr">
@@ -15027,6 +17682,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F532" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" s="2" t="inlineStr">
@@ -15054,6 +17714,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F533" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" s="2" t="inlineStr">
@@ -15081,6 +17746,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F534" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" s="2" t="inlineStr">
@@ -15108,6 +17778,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F535" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="536" ht="27" customHeight="1">
       <c r="A536" s="2" t="inlineStr">
@@ -15127,12 +17802,17 @@
       </c>
       <c r="D536" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Gleichmäßigkeit und der musikalisch sinnvolle Einsatz des Vibratos** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Gleichmäßigkeit und der musikalisch sinnvolle Einsatz des Vibratos bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E536" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the evenness and musically appropriate use of the vibrato for this pupil is:</t>
+          <t>**Compared to the last lesson**, the evenness and musically appropriate use of the vibrato for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F536" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -15162,6 +17842,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F537" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" s="2" t="inlineStr">
@@ -15189,6 +17874,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F538" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" s="2" t="inlineStr">
@@ -15216,6 +17906,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F539" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" s="2" t="inlineStr">
@@ -15243,6 +17938,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F540" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" s="2" t="inlineStr">
@@ -15270,6 +17970,11 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
+      <c r="F541" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" s="2" t="inlineStr">
@@ -15289,15 +17994,20 @@
       </c>
       <c r="D542" s="4" t="inlineStr">
         <is>
-          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel** des/der Schüler/in zu?</t>
+          <t>Welche dieser Aussagen trifft auf **das Klavierspiel** des/der Schüler/in zu?</t>
         </is>
       </c>
       <c r="E542" s="4" t="inlineStr">
         <is>
-          <t>Which of the following statements applies to the pupil’s instrumental playing?</t>
-        </is>
-      </c>
-      <c r="F542" t="inlineStr">
+          <t>Which of the following statements applies to the pupil’s **piano playing**?</t>
+        </is>
+      </c>
+      <c r="F542" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
         <is>
           <t>Wrigley &amp; Emmerson (2013) – PERS Piano ("physically: comfortable and at ease")</t>
         </is>
@@ -15329,6 +18039,11 @@
           <t>Both hands are predominantly uncoordinated. The interplay consistently seems uncertain.</t>
         </is>
       </c>
+      <c r="F543" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="544" ht="27" customHeight="1">
       <c r="A544" s="2" t="inlineStr">
@@ -15356,6 +18071,11 @@
           <t>Both hands are often not well coordinated. The interplay seems correspondingly uncertain.</t>
         </is>
       </c>
+      <c r="F544" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="545" ht="27" customHeight="1">
       <c r="A545" s="2" t="inlineStr">
@@ -15383,6 +18103,11 @@
           <t>Both hands are partially coordinated. The interplay recurringly seems uneven.</t>
         </is>
       </c>
+      <c r="F545" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="546" ht="27" customHeight="1">
       <c r="A546" s="2" t="inlineStr">
@@ -15410,6 +18135,11 @@
           <t>Both hands are largely coordinated. The interplay mostly seems natural, with isolated minor inconsistencies.</t>
         </is>
       </c>
+      <c r="F546" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="547" ht="27" customHeight="1">
       <c r="A547" s="2" t="inlineStr">
@@ -15437,6 +18167,11 @@
           <t>Both hands are consistently perfectly coordinated. The interplay appears natural and effortless.</t>
         </is>
       </c>
+      <c r="F547" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="548" ht="27" customHeight="1">
       <c r="A548" s="2" t="inlineStr">
@@ -15456,12 +18191,17 @@
       </c>
       <c r="D548" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Abstimmung beider Hände** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Abstimmung beider Hände bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E548" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the coordination between both hands for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the coordination between both hands for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F548" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -15491,6 +18231,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F549" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" s="2" t="inlineStr">
@@ -15518,6 +18263,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F550" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" s="2" t="inlineStr">
@@ -15545,6 +18295,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F551" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" s="2" t="inlineStr">
@@ -15572,6 +18327,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F552" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" s="2" t="inlineStr">
@@ -15599,6 +18359,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F553" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="554" ht="27" customHeight="1">
       <c r="A554" s="2" t="inlineStr">
@@ -15618,12 +18383,17 @@
       </c>
       <c r="D554" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Abstimmung beider Hände** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Abstimmung beider Hände bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E554" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the coordination between both hands for this pupil is:</t>
+          <t>**Compared to the last lesson**, the coordination between both hands for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F554" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -15653,6 +18423,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F555" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" s="2" t="inlineStr">
@@ -15680,6 +18455,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F556" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" s="2" t="inlineStr">
@@ -15707,6 +18487,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F557" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" s="2" t="inlineStr">
@@ -15734,6 +18519,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F558" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" s="2" t="inlineStr">
@@ -15761,6 +18551,11 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
+      <c r="F559" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" s="2" t="inlineStr">
@@ -15780,15 +18575,20 @@
       </c>
       <c r="D560" s="4" t="inlineStr">
         <is>
-          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel** des/der Schüler/in zu?</t>
+          <t>Welche dieser Aussagen trifft auf **das Klavierspiel** des/der Schüler/in zu?</t>
         </is>
       </c>
       <c r="E560" s="4" t="inlineStr">
         <is>
-          <t>Which of the following statements applies to the pupil’s instrumental playing?</t>
-        </is>
-      </c>
-      <c r="F560" t="inlineStr">
+          <t>Which of the following statements applies to the pupil’s **piano playing**?</t>
+        </is>
+      </c>
+      <c r="F560" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
         <is>
           <t>Barry (2009) – Sample Assessment Rubric for Preparatory Piano Exam, Kategorie Fingering</t>
         </is>
@@ -15820,6 +18620,11 @@
           <t>The fingering used is predominantly inefficient. A fluid performance rarely succeeds.</t>
         </is>
       </c>
+      <c r="F561" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="562" ht="27" customHeight="1">
       <c r="A562" s="2" t="inlineStr">
@@ -15847,6 +18652,11 @@
           <t>The fingering used is often inefficient and noticeably impairs phrasing and performance.</t>
         </is>
       </c>
+      <c r="F562" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="563" ht="27" customHeight="1">
       <c r="A563" s="2" t="inlineStr">
@@ -15874,6 +18684,11 @@
           <t>The fingering used is partially efficient. Phrasing is recurringly impaired.</t>
         </is>
       </c>
+      <c r="F563" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="564" ht="27" customHeight="1">
       <c r="A564" s="2" t="inlineStr">
@@ -15901,6 +18716,11 @@
           <t>The fingering used is largely efficient and supports the phrasing. Isolated minor interruptions occur.</t>
         </is>
       </c>
+      <c r="F564" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="565" ht="27" customHeight="1">
       <c r="A565" s="2" t="inlineStr">
@@ -15928,6 +18748,11 @@
           <t>The fingering used is consistently efficient, supports the phrasing and enables a fluid performance.</t>
         </is>
       </c>
+      <c r="F565" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="566" ht="27" customHeight="1">
       <c r="A566" s="2" t="inlineStr">
@@ -15947,12 +18772,17 @@
       </c>
       <c r="D566" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Effizienz des Fingersatzes** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Effizienz des Fingersatzes bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E566" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the efficiency of the fingering for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the efficiency of the fingering for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F566" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -15982,6 +18812,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F567" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" s="2" t="inlineStr">
@@ -16009,6 +18844,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F568" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" s="2" t="inlineStr">
@@ -16036,6 +18876,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F569" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" s="2" t="inlineStr">
@@ -16063,6 +18908,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F570" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" s="2" t="inlineStr">
@@ -16090,6 +18940,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F571" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="572" ht="27" customHeight="1">
       <c r="A572" s="2" t="inlineStr">
@@ -16109,12 +18964,17 @@
       </c>
       <c r="D572" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Effizienz des Fingersatzes** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Effizienz des Fingersatzes bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E572" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the efficiency of the fingering for this pupil is:</t>
+          <t>**Compared to the last lesson**, the efficiency of the fingering for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F572" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -16144,6 +19004,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F573" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" s="2" t="inlineStr">
@@ -16171,6 +19036,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F574" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" s="2" t="inlineStr">
@@ -16198,6 +19068,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F575" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" s="2" t="inlineStr">
@@ -16225,6 +19100,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F576" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" s="2" t="inlineStr">
@@ -16252,6 +19132,11 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
+      <c r="F577" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" s="2" t="inlineStr">
@@ -16271,15 +19156,20 @@
       </c>
       <c r="D578" s="4" t="inlineStr">
         <is>
-          <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel** des/der Schüler/in zu?</t>
+          <t>Welche dieser Aussagen trifft auf **das Klavierspiel** des/der Schüler/in zu?</t>
         </is>
       </c>
       <c r="E578" s="4" t="inlineStr">
         <is>
-          <t>Which of the following statements applies to the pupil’s instrumental playing?</t>
-        </is>
-      </c>
-      <c r="F578" t="inlineStr">
+          <t>Which of the following statements applies to the pupil’s **piano playing**?</t>
+        </is>
+      </c>
+      <c r="F578" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
         <is>
           <t>Wrigley &amp; Emmerson (2013) – PERS Piano ("texture: clear")</t>
         </is>
@@ -16311,6 +19201,11 @@
           <t>The melodic line predominantly does not stand out from the accompaniment. Balance between the parts is largely absent.</t>
         </is>
       </c>
+      <c r="F579" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="580" ht="27" customHeight="1">
       <c r="A580" s="2" t="inlineStr">
@@ -16338,6 +19233,11 @@
           <t>The melodic line often does not clearly stand out from the accompaniment. The balance is correspondingly uneven.</t>
         </is>
       </c>
+      <c r="F580" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="581" ht="27" customHeight="1">
       <c r="A581" s="2" t="inlineStr">
@@ -16365,6 +19265,11 @@
           <t>The melodic line partially stands out from the accompaniment. The balance between the parts is recurringly uneven.</t>
         </is>
       </c>
+      <c r="F581" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="582" ht="27" customHeight="1">
       <c r="A582" s="2" t="inlineStr">
@@ -16392,6 +19297,11 @@
           <t>The melodic line largely stands out from the accompaniment. The balance is mostly well-balanced, with isolated minor fluctuations.</t>
         </is>
       </c>
+      <c r="F582" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="583" ht="27" customHeight="1">
       <c r="A583" s="2" t="inlineStr">
@@ -16419,6 +19329,11 @@
           <t>The melodic line consistently stands out clearly from the accompaniment. The balance between the parts is consistently well-balanced.</t>
         </is>
       </c>
+      <c r="F583" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="584" ht="27" customHeight="1">
       <c r="A584" s="2" t="inlineStr">
@@ -16438,12 +19353,17 @@
       </c>
       <c r="D584" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Balance zwischen melodischer Linie und Begleitung** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Balance zwischen melodischer Linie und Begleitung bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E584" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the balance between the melodic line and the accompaniment for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the balance between the melodic line and the accompaniment for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F584" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -16473,6 +19393,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F585" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
@@ -16500,6 +19425,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F586" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" s="2" t="inlineStr">
@@ -16527,6 +19457,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F587" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
@@ -16554,6 +19489,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F588" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" s="2" t="inlineStr">
@@ -16581,6 +19521,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F589" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="590" ht="27" customHeight="1">
       <c r="A590" s="2" t="inlineStr">
@@ -16600,12 +19545,17 @@
       </c>
       <c r="D590" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Balance zwischen melodischer Linie und Begleitung** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Balance zwischen melodischer Linie und Begleitung bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E590" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the balance between the melodic line and the accompaniment for this pupil is:</t>
+          <t>**Compared to the last lesson**, the balance between the melodic line and the accompaniment for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F590" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -16635,6 +19585,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F591" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
@@ -16662,6 +19617,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F592" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" s="2" t="inlineStr">
@@ -16689,6 +19649,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F593" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
@@ -16716,6 +19681,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F594" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" s="2" t="inlineStr">
@@ -16743,8 +19713,13 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
-    </row>
-    <row r="596">
+      <c r="F595" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="596" ht="27" customHeight="1">
       <c r="A596" s="2" t="inlineStr">
         <is>
           <t>MLP_0035_L3_PROMPT</t>
@@ -16767,10 +19742,15 @@
       </c>
       <c r="E596" s="4" t="inlineStr">
         <is>
-          <t>Which of the following statements applies to the pupil’s instrumental playing?</t>
-        </is>
-      </c>
-      <c r="F596" t="inlineStr">
+          <t>Which of the following statements applies to the pupil’s **instrumental playing**?</t>
+        </is>
+      </c>
+      <c r="F596" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
         <is>
           <t>Saunders &amp; Holahan (1997) – Tempo (s. o., 0007)</t>
         </is>
@@ -16802,6 +19782,11 @@
           <t>The playing tempo is consistently well below the tempo indicated by the piece.</t>
         </is>
       </c>
+      <c r="F597" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="598" ht="27" customHeight="1">
       <c r="A598" s="2" t="inlineStr">
@@ -16829,6 +19814,11 @@
           <t>The playing tempo is often well below the tempo indicated by the piece.</t>
         </is>
       </c>
+      <c r="F598" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="599" ht="27" customHeight="1">
       <c r="A599" s="2" t="inlineStr">
@@ -16856,6 +19846,11 @@
           <t>The playing tempo partially matches the indicated tempo. Several passages are played noticeably slower.</t>
         </is>
       </c>
+      <c r="F599" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="600" ht="27" customHeight="1">
       <c r="A600" s="2" t="inlineStr">
@@ -16883,6 +19878,11 @@
           <t>The playing tempo largely matches the indicated tempo. Individual passages are played noticeably slower.</t>
         </is>
       </c>
+      <c r="F600" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="601" ht="27" customHeight="1">
       <c r="A601" s="2" t="inlineStr">
@@ -16910,6 +19910,11 @@
           <t>The playing tempo consistently matches the tempo indicated by the piece, even in technically demanding passages.</t>
         </is>
       </c>
+      <c r="F601" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="602" ht="27" customHeight="1">
       <c r="A602" s="2" t="inlineStr">
@@ -16929,12 +19934,17 @@
       </c>
       <c r="D602" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Tempotreue** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Tempotreue bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E602" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the tempo accuracy for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the tempo accuracy for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F602" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -16964,6 +19974,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F603" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
@@ -16991,6 +20006,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F604" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" s="2" t="inlineStr">
@@ -17018,6 +20038,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F605" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
@@ -17045,6 +20070,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F606" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" s="2" t="inlineStr">
@@ -17072,6 +20102,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F607" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="608" ht="27" customHeight="1">
       <c r="A608" s="2" t="inlineStr">
@@ -17091,12 +20126,17 @@
       </c>
       <c r="D608" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Tempotreue** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Tempotreue bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E608" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the tempo accuracy for this pupil is:</t>
+          <t>**Compared to the last lesson**, the tempo accuracy for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F608" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -17126,6 +20166,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F609" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" s="2" t="inlineStr">
@@ -17153,6 +20198,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F610" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" s="2" t="inlineStr">
@@ -17180,6 +20230,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F611" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" s="2" t="inlineStr">
@@ -17207,6 +20262,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F612" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" s="2" t="inlineStr">
@@ -17234,8 +20294,13 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
-    </row>
-    <row r="614">
+      <c r="F613" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="614" ht="27" customHeight="1">
       <c r="A614" s="2" t="inlineStr">
         <is>
           <t>MLP_0036_L3_PROMPT</t>
@@ -17258,10 +20323,15 @@
       </c>
       <c r="E614" s="4" t="inlineStr">
         <is>
-          <t>Which of the following statements applies to the pupil’s instrumental playing?</t>
-        </is>
-      </c>
-      <c r="F614" t="inlineStr">
+          <t>Which of the following statements applies to the pupil’s **instrumental playing**?</t>
+        </is>
+      </c>
+      <c r="F614" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
         <is>
           <t>Barry (2009) – Sample Rubric, Kategorie Memorization; auch Wrigley &amp; Emmerson (2013), PERS ("memory: accurate, secure and reliable", in allen 5 Instrumentenfamilien)</t>
         </is>
@@ -17293,6 +20363,11 @@
           <t>The piece is consistently played from sheet music.</t>
         </is>
       </c>
+      <c r="F615" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="616" ht="27" customHeight="1">
       <c r="A616" s="2" t="inlineStr">
@@ -17320,6 +20395,11 @@
           <t>The piece is played from memory only in short sections. It is mostly played from sheet music.</t>
         </is>
       </c>
+      <c r="F616" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="617" ht="27" customHeight="1">
       <c r="A617" s="2" t="inlineStr">
@@ -17347,6 +20427,11 @@
           <t>The piece is partially played from memory. The sheet music is consulted in several sections.</t>
         </is>
       </c>
+      <c r="F617" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="618" ht="27" customHeight="1">
       <c r="A618" s="2" t="inlineStr">
@@ -17374,6 +20459,11 @@
           <t>The piece is largely played from memory. The sheet music is briefly consulted in isolated moments.</t>
         </is>
       </c>
+      <c r="F618" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" s="2" t="inlineStr">
@@ -17401,6 +20491,11 @@
           <t>The piece is consistently played confidently and entirely from memory.</t>
         </is>
       </c>
+      <c r="F619" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="620" ht="27" customHeight="1">
       <c r="A620" s="2" t="inlineStr">
@@ -17420,12 +20515,17 @@
       </c>
       <c r="D620" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist der **Grad des Auswendigspiels** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist der Grad des Auswendigspiels bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E620" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the degree of memorisation for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the degree of memorisation for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F620" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -17455,6 +20555,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F621" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" s="2" t="inlineStr">
@@ -17482,6 +20587,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F622" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="623">
       <c r="A623" s="2" t="inlineStr">
@@ -17509,6 +20619,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F623" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" s="2" t="inlineStr">
@@ -17536,6 +20651,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F624" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="625">
       <c r="A625" s="2" t="inlineStr">
@@ -17563,6 +20683,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F625" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="626" ht="27" customHeight="1">
       <c r="A626" s="2" t="inlineStr">
@@ -17582,12 +20707,17 @@
       </c>
       <c r="D626" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist der **Grad des Auswendigspiels** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist der Grad des Auswendigspiels bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E626" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the degree of memorisation for this pupil is:</t>
+          <t>**Compared to the last lesson**, the degree of memorisation for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F626" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -17617,6 +20747,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F627" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" s="2" t="inlineStr">
@@ -17644,6 +20779,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F628" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" s="2" t="inlineStr">
@@ -17671,6 +20811,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F629" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" s="2" t="inlineStr">
@@ -17698,6 +20843,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F630" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" s="2" t="inlineStr">
@@ -17725,8 +20875,13 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
-    </row>
-    <row r="632">
+      <c r="F631" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="632" ht="27" customHeight="1">
       <c r="A632" s="2" t="inlineStr">
         <is>
           <t>MLP_0037_L3_PROMPT</t>
@@ -17749,10 +20904,15 @@
       </c>
       <c r="E632" s="4" t="inlineStr">
         <is>
-          <t>Which of the following statements applies to the pupil’s instrumental playing?</t>
-        </is>
-      </c>
-      <c r="F632" t="inlineStr">
+          <t>Which of the following statements applies to the pupil’s **instrumental playing**?</t>
+        </is>
+      </c>
+      <c r="F632" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
         <is>
           <t>Mills (1987) – Item 8 ("performer's technical problems were distracting/hardly noticeable")</t>
         </is>
@@ -17784,6 +20944,11 @@
           <t>Even minor distractions consistently lead to mistakes while playing.</t>
         </is>
       </c>
+      <c r="F633" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" s="2" t="inlineStr">
@@ -17811,6 +20976,11 @@
           <t>Minor distractions often lead to mistakes while playing.</t>
         </is>
       </c>
+      <c r="F634" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="635" ht="27" customHeight="1">
       <c r="A635" s="2" t="inlineStr">
@@ -17838,6 +21008,11 @@
           <t>Concentration is partially impaired by minor distractions, which recurringly leads to mistakes.</t>
         </is>
       </c>
+      <c r="F635" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="636" ht="27" customHeight="1">
       <c r="A636" s="2" t="inlineStr">
@@ -17865,6 +21040,11 @@
           <t>Concentration largely remains stable while playing. Minor distractions only occasionally lead to small mistakes.</t>
         </is>
       </c>
+      <c r="F636" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="637" ht="27" customHeight="1">
       <c r="A637" s="2" t="inlineStr">
@@ -17892,6 +21072,11 @@
           <t>Concentration consistently remains stable while playing, even with minor distractions. No mistakes result from them.</t>
         </is>
       </c>
+      <c r="F637" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="638" ht="27" customHeight="1">
       <c r="A638" s="2" t="inlineStr">
@@ -17911,12 +21096,17 @@
       </c>
       <c r="D638" s="4" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist die **Konzentrationsstabilität bei Ablenkungen** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist die Konzentrationsstabilität bei Ablenkungen bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E638" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the stability of concentration under distraction for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the stability of concentration under distraction for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F638" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -17946,6 +21136,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F639" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" s="2" t="inlineStr">
@@ -17973,6 +21168,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F640" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" s="2" t="inlineStr">
@@ -18000,6 +21200,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F641" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="A642" s="2" t="inlineStr">
@@ -18027,6 +21232,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F642" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" s="2" t="inlineStr">
@@ -18054,6 +21264,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F643" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="644" ht="27" customHeight="1">
       <c r="A644" s="2" t="inlineStr">
@@ -18073,12 +21288,17 @@
       </c>
       <c r="D644" s="10" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist die **Konzentrationsstabilität bei Ablenkungen** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist die Konzentrationsstabilität bei Ablenkungen bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E644" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the stability of concentration under distraction for this pupil is:</t>
+          <t>**Compared to the last lesson**, the stability of concentration under distraction for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F644" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -18108,6 +21328,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F645" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="646">
       <c r="A646" s="2" t="inlineStr">
@@ -18135,6 +21360,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F646" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="A647" s="2" t="inlineStr">
@@ -18162,6 +21392,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F647" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="A648" s="2" t="inlineStr">
@@ -18189,6 +21424,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F648" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="649">
       <c r="A649" s="2" t="inlineStr">
@@ -18216,8 +21456,13 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
-    </row>
-    <row r="650">
+      <c r="F649" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="650" ht="27" customHeight="1">
       <c r="A650" s="2" t="inlineStr">
         <is>
           <t>MLP_0038_L3_PROMPT</t>
@@ -18233,17 +21478,22 @@
           <t>Ebene 3 - kriterienbezogen</t>
         </is>
       </c>
-      <c r="D650" s="10" t="inlineStr">
+      <c r="D650" s="4" t="inlineStr">
         <is>
           <t>Welche dieser Aussagen trifft auf **das Instrumentalspiel** des/der Schüler/in zu?</t>
         </is>
       </c>
       <c r="E650" s="4" t="inlineStr">
         <is>
-          <t>Which of the following statements applies to the pupil’s instrumental playing?</t>
-        </is>
-      </c>
-      <c r="F650" t="inlineStr">
+          <t>Which of the following statements applies to the pupil’s **instrumental playing**?</t>
+        </is>
+      </c>
+      <c r="F650" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
         <is>
           <t>Russell (2015) – kausaler Zusammenhang Technik → musikalischer Ausdruck ("technique demonstrated direct effects on overall quality and expression")</t>
         </is>
@@ -18275,6 +21525,11 @@
           <t>The focus while playing is entirely on hitting the right notes. Musical shaping does not take place.</t>
         </is>
       </c>
+      <c r="F651" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="652" ht="27" customHeight="1">
       <c r="A652" s="2" t="inlineStr">
@@ -18302,6 +21557,11 @@
           <t>The focus while playing is predominantly on hitting the right notes. Musical shaping recedes into the background.</t>
         </is>
       </c>
+      <c r="F652" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="653" ht="27" customHeight="1">
       <c r="A653" s="2" t="inlineStr">
@@ -18329,6 +21589,11 @@
           <t>The focus while playing is partially on musical shaping and partially still on hitting the right notes.</t>
         </is>
       </c>
+      <c r="F653" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="654" ht="40.5" customHeight="1">
       <c r="A654" s="2" t="inlineStr">
@@ -18356,6 +21621,11 @@
           <t>The focus while playing is largely on musical shaping. Hitting the right notes only occasionally requires conscious attention.</t>
         </is>
       </c>
+      <c r="F654" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="655" ht="27" customHeight="1">
       <c r="A655" s="2" t="inlineStr">
@@ -18383,6 +21653,11 @@
           <t>The focus while playing is consistently on musical shaping. Hitting the right notes is fully automatised.</t>
         </is>
       </c>
+      <c r="F655" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="656" ht="40.5" customHeight="1">
       <c r="A656" s="2" t="inlineStr">
@@ -18402,12 +21677,17 @@
       </c>
       <c r="D656" s="10" t="inlineStr">
         <is>
-          <t>Im Vergleich zu Schüler/innen auf vergleichbarem Niveau ist der **Fokus auf musikalische Gestaltung gegenüber Tonsicherheit** bei diesem/dieser Schüler/in:</t>
+          <t>**Im Vergleich zu Schüler/innen auf vergleichbarem Niveau** ist der Fokus auf musikalische Gestaltung gegenüber Tonsicherheit bei diesem/dieser Schüler/in:</t>
         </is>
       </c>
       <c r="E656" s="4" t="inlineStr">
         <is>
-          <t>Compared to pupils at a similar level, the focus on musical shaping versus note accuracy for this pupil is:</t>
+          <t>**Compared to pupils at a similar level**, the focus on musical shaping versus note accuracy for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F656" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -18437,6 +21717,11 @@
           <t>Clearly worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F657" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" s="2" t="inlineStr">
@@ -18464,6 +21749,11 @@
           <t>Worse than comparable pupils</t>
         </is>
       </c>
+      <c r="F658" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" s="2" t="inlineStr">
@@ -18491,6 +21781,11 @@
           <t>The same as comparable pupils</t>
         </is>
       </c>
+      <c r="F659" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" s="2" t="inlineStr">
@@ -18518,6 +21813,11 @@
           <t>Better than comparable pupils</t>
         </is>
       </c>
+      <c r="F660" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="A661" s="2" t="inlineStr">
@@ -18545,6 +21845,11 @@
           <t>Much better than comparable pupils</t>
         </is>
       </c>
+      <c r="F661" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="662" ht="27" customHeight="1">
       <c r="A662" s="2" t="inlineStr">
@@ -18564,12 +21869,17 @@
       </c>
       <c r="D662" s="10" t="inlineStr">
         <is>
-          <t>Im Vergleich zur letzten Unterrichtseinheit ist der **Fokus auf musikalische Gestaltung gegenüber Tonsicherheit** bei dieser/diesem Schüler/in:</t>
+          <t>**Im Vergleich zur letzten Unterrichtseinheit** ist der Fokus auf musikalische Gestaltung gegenüber Tonsicherheit bei dieser/diesem Schüler/in:</t>
         </is>
       </c>
       <c r="E662" s="4" t="inlineStr">
         <is>
-          <t>Compared to the last lesson, the focus on musical shaping versus note accuracy for this pupil is:</t>
+          <t>**Compared to the last lesson**, the focus on musical shaping versus note accuracy for this pupil is:</t>
+        </is>
+      </c>
+      <c r="F662" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -18599,6 +21909,11 @@
           <t>Clearly worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F663" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="664">
       <c r="A664" s="2" t="inlineStr">
@@ -18626,6 +21941,11 @@
           <t>Worse than in the last lesson</t>
         </is>
       </c>
+      <c r="F664" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="665">
       <c r="A665" s="2" t="inlineStr">
@@ -18653,6 +21973,11 @@
           <t>The same as in the last lesson</t>
         </is>
       </c>
+      <c r="F665" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="666">
       <c r="A666" s="2" t="inlineStr">
@@ -18680,6 +22005,11 @@
           <t>Better than in the last lesson</t>
         </is>
       </c>
+      <c r="F666" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="667">
       <c r="A667" s="2" t="inlineStr">
@@ -18707,6 +22037,11 @@
           <t>Much better than in the last lesson</t>
         </is>
       </c>
+      <c r="F667" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="668" ht="27" customHeight="1">
       <c r="A668" s="2" t="inlineStr">
@@ -18734,6 +22069,11 @@
           <t>Evaluate **the overall quality** of the student’s instrumental performance on the following pages.</t>
         </is>
       </c>
+      <c r="F668" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="669" ht="27" customHeight="1">
       <c r="A669" s="2" t="inlineStr">
@@ -18761,6 +22101,11 @@
           <t>Evaluate **the technical quality** of the student’s instrumental performance on the following pages.</t>
         </is>
       </c>
+      <c r="F669" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="670" ht="27" customHeight="1">
       <c r="A670" s="2" t="inlineStr">
@@ -18788,6 +22133,11 @@
           <t>Evaluate **the expressive quality** of the student’s instrumental performance on the following pages.</t>
         </is>
       </c>
+      <c r="F670" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
     </row>
     <row r="671" ht="27" customHeight="1">
       <c r="A671" s="2" t="inlineStr">
@@ -18813,6 +22163,11 @@
       <c r="E671" s="11" t="inlineStr">
         <is>
           <t>Evaluate **the instrument-specific quality** of the student’s instrumental performance on the following pages.</t>
+        </is>
+      </c>
+      <c r="F671" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
